--- a/excel-files/MUNTINLUPA/LAKEVIEW INTEGRATED SCHOOL.xlsx
+++ b/excel-files/MUNTINLUPA/LAKEVIEW INTEGRATED SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85347B63-96CD-4991-932B-DE8F4A620535}"/>
+  <xr:revisionPtr revIDLastSave="582" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03BE11AA-131B-4018-8764-F73DDC6344BC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -631,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -759,6 +759,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3731,17 +3734,21 @@
         <v>352</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+        <v>404</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.5">
@@ -4154,17 +4161,21 @@
         <v>381</v>
       </c>
       <c r="D29" s="1">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+        <v>421</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4319,7 +4330,7 @@
         <v>405</v>
       </c>
       <c r="E36" s="1">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>9</v>
@@ -4372,17 +4383,21 @@
         <v>350</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4684,13 +4699,17 @@
         <v>638</v>
       </c>
       <c r="D52" s="10">
-        <v>0</v>
-      </c>
-      <c r="E52" s="10"/>
-      <c r="F52" s="12"/>
+        <v>565</v>
+      </c>
+      <c r="E52" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="G52" s="3">
         <f t="shared" si="10"/>
-        <v>638</v>
+        <v>73</v>
       </c>
       <c r="H52" s="4">
         <f t="shared" si="11"/>
@@ -4736,13 +4755,17 @@
         <v>638</v>
       </c>
       <c r="D54" s="10">
-        <v>0</v>
-      </c>
-      <c r="E54" s="10"/>
-      <c r="F54" s="12"/>
+        <v>565</v>
+      </c>
+      <c r="E54" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="G54" s="3">
         <f t="shared" si="10"/>
-        <v>638</v>
+        <v>73</v>
       </c>
       <c r="H54" s="4">
         <f t="shared" si="11"/>
@@ -4986,13 +5009,17 @@
         <v>624</v>
       </c>
       <c r="D64" s="10">
-        <v>0</v>
-      </c>
-      <c r="E64" s="10"/>
-      <c r="F64" s="12"/>
+        <v>453</v>
+      </c>
+      <c r="E64" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="G64" s="3">
         <f t="shared" si="12"/>
-        <v>624</v>
+        <v>171</v>
       </c>
       <c r="H64" s="4">
         <f t="shared" si="13"/>
@@ -5034,13 +5061,17 @@
         <v>624</v>
       </c>
       <c r="D66" s="10">
-        <v>0</v>
-      </c>
-      <c r="E66" s="10"/>
-      <c r="F66" s="12"/>
+        <v>453</v>
+      </c>
+      <c r="E66" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="G66" s="3">
         <f t="shared" si="12"/>
-        <v>624</v>
+        <v>171</v>
       </c>
       <c r="H66" s="4">
         <f t="shared" si="13"/>
@@ -5776,14 +5807,14 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C1:E1 C2:D5 C6:E21 C22:D27 C28:E30 C31:D37 C38:E50 C60:E60 C51:D59 C70:E98 C61:D69 E68:E69" name="Textbooks"/>
-    <protectedRange sqref="F1 F6:F21 F28:F30 F38:F50 F60 F68:F98" name="SOURCE"/>
+    <protectedRange sqref="F1 F6:F21 F28:F30 F39:F50 F60 F68:F98" name="SOURCE"/>
     <protectedRange sqref="E2:E5" name="Textbooks_1"/>
     <protectedRange sqref="F2:F5" name="SOURCE_1"/>
     <protectedRange sqref="E22:E27" name="Textbooks_1_2"/>
     <protectedRange sqref="F22:F27" name="SOURCE_1_2"/>
     <protectedRange sqref="E31:E37" name="Textbooks_2"/>
     <protectedRange sqref="F32:F34" name="SOURCE_2"/>
-    <protectedRange sqref="F31 F35:F37" name="SOURCE_1_2_1"/>
+    <protectedRange sqref="F31 F35:F38" name="SOURCE_1_2_1"/>
     <protectedRange sqref="E51:E59" name="Textbooks_3"/>
     <protectedRange sqref="F51:F59" name="SOURCE_3"/>
     <protectedRange sqref="E61:E67" name="Textbooks_4"/>
@@ -5791,10 +5822,10 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E2:E6 E21:E29 E31:E39 E51:E59 E41:E49 E91:E98 E71:E79 E81:E89 E8:E12 E61:E69" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F2:F6 F21:F29 F41:F49 F31:F39 F51:F59 F71:F79 F81:F89 F91:F98 F8:F12 F61:F69" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F2:F6 F21:F29 F41:F49 F61:F69 F51:F59 F71:F79 F81:F89 F91:F98 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5810,7 +5841,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5985,7 +6016,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2976</v>
       </c>
-      <c r="K3" s="34"/>
+      <c r="K3" s="34">
+        <v>0</v>
+      </c>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="5">
@@ -6000,7 +6033,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2976</v>
       </c>
-      <c r="Q3" s="34"/>
+      <c r="Q3" s="34">
+        <v>0</v>
+      </c>
       <c r="R3" s="32"/>
       <c r="S3" s="34"/>
       <c r="T3" s="34">
@@ -6076,7 +6111,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K5" s="5"/>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
@@ -6091,7 +6128,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q5" s="5"/>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
@@ -6106,7 +6145,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W5" s="5"/>
+      <c r="W5" s="5">
+        <v>0</v>
+      </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
@@ -6149,7 +6190,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K6" s="5"/>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
@@ -6164,7 +6207,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q6" s="5"/>
+      <c r="Q6" s="5">
+        <v>0</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
@@ -6179,7 +6224,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W6" s="5"/>
+      <c r="W6" s="5">
+        <v>0</v>
+      </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
@@ -6222,7 +6269,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K7" s="5"/>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
@@ -6237,7 +6286,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q7" s="5"/>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
@@ -6252,7 +6303,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W7" s="5"/>
+      <c r="W7" s="5">
+        <v>0</v>
+      </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
@@ -6295,7 +6348,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K8" s="5"/>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
@@ -6310,7 +6365,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q8" s="5"/>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
@@ -6325,7 +6382,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W8" s="5"/>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
@@ -6368,7 +6427,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K9" s="5"/>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
@@ -6383,7 +6444,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q9" s="5"/>
+      <c r="Q9" s="5">
+        <v>0</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
@@ -6398,7 +6461,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W9" s="5"/>
+      <c r="W9" s="5">
+        <v>0</v>
+      </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
@@ -6441,7 +6506,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K10" s="5"/>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
@@ -6456,7 +6523,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q10" s="5"/>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
@@ -6471,7 +6540,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W10" s="5"/>
+      <c r="W10" s="5">
+        <v>0</v>
+      </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
@@ -6514,7 +6585,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K11" s="5"/>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
       <c r="L11" s="1"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5">
@@ -6529,7 +6602,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q11" s="5"/>
+      <c r="Q11" s="5">
+        <v>0</v>
+      </c>
       <c r="R11" s="1"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
@@ -6544,7 +6619,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W11" s="5"/>
+      <c r="W11" s="5">
+        <v>0</v>
+      </c>
       <c r="X11" s="1"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5">
@@ -6587,7 +6664,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K12" s="5"/>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
@@ -6602,7 +6681,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q12" s="5"/>
+      <c r="Q12" s="5">
+        <v>0</v>
+      </c>
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
@@ -6617,7 +6698,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W12" s="5"/>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
@@ -6673,7 +6756,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="K14" s="5"/>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5">
@@ -6688,7 +6773,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q14" s="5"/>
+      <c r="Q14" s="5">
+        <v>0</v>
+      </c>
       <c r="R14" s="1"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
@@ -6703,7 +6790,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W14" s="5"/>
+      <c r="W14" s="5">
+        <v>0</v>
+      </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
@@ -6746,7 +6835,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="K15" s="5"/>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5">
@@ -6761,7 +6852,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q15" s="5"/>
+      <c r="Q15" s="5">
+        <v>0</v>
+      </c>
       <c r="R15" s="1"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
@@ -6776,7 +6869,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W15" s="5"/>
+      <c r="W15" s="5">
+        <v>0</v>
+      </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
@@ -6823,7 +6918,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="K16" s="5"/>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="5" t="s">
         <v>62</v>
@@ -6840,7 +6937,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q16" s="5"/>
+      <c r="Q16" s="5">
+        <v>0</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5">
@@ -6855,7 +6954,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W16" s="5"/>
+      <c r="W16" s="5">
+        <v>0</v>
+      </c>
       <c r="X16" s="1"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5">
@@ -6923,7 +7024,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q17" s="5"/>
+      <c r="Q17" s="5">
+        <v>0</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
@@ -6938,7 +7041,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W17" s="5"/>
+      <c r="W17" s="5">
+        <v>0</v>
+      </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
@@ -7006,7 +7111,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q18" s="5"/>
+      <c r="Q18" s="5">
+        <v>0</v>
+      </c>
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
@@ -7021,7 +7128,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W18" s="5"/>
+      <c r="W18" s="5">
+        <v>0</v>
+      </c>
       <c r="X18" s="1"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5">
@@ -7089,7 +7198,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q19" s="5"/>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
@@ -7104,7 +7215,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W19" s="5"/>
+      <c r="W19" s="5">
+        <v>0</v>
+      </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
@@ -7172,7 +7285,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q20" s="5"/>
+      <c r="Q20" s="5">
+        <v>0</v>
+      </c>
       <c r="R20" s="1"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5">
@@ -7187,7 +7302,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W20" s="5"/>
+      <c r="W20" s="5">
+        <v>0</v>
+      </c>
       <c r="X20" s="1"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="5">
@@ -7230,7 +7347,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="K21" s="5"/>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
       <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
@@ -7245,7 +7364,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q21" s="5"/>
+      <c r="Q21" s="5">
+        <v>0</v>
+      </c>
       <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
@@ -7260,7 +7381,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W21" s="5"/>
+      <c r="W21" s="5">
+        <v>0</v>
+      </c>
       <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
@@ -7317,7 +7440,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K23" s="5"/>
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5">
@@ -7332,7 +7457,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q23" s="5"/>
+      <c r="Q23" s="5">
+        <v>0</v>
+      </c>
       <c r="R23" s="1"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
@@ -7347,7 +7474,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W23" s="5"/>
+      <c r="W23" s="5">
+        <v>0</v>
+      </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5">
@@ -7390,7 +7519,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K24" s="5"/>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
       <c r="L24" s="1"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5">
@@ -7405,7 +7536,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q24" s="5"/>
+      <c r="Q24" s="5">
+        <v>0</v>
+      </c>
       <c r="R24" s="1"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5">
@@ -7420,7 +7553,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W24" s="5"/>
+      <c r="W24" s="5">
+        <v>0</v>
+      </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5">
@@ -7467,7 +7602,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K25" s="5"/>
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5">
@@ -7482,7 +7619,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q25" s="5"/>
+      <c r="Q25" s="5">
+        <v>0</v>
+      </c>
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
@@ -7497,7 +7636,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W25" s="5"/>
+      <c r="W25" s="5">
+        <v>0</v>
+      </c>
       <c r="X25" s="1"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
@@ -7544,7 +7685,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K26" s="5"/>
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5">
@@ -7559,7 +7702,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q26" s="5"/>
+      <c r="Q26" s="5">
+        <v>0</v>
+      </c>
       <c r="R26" s="1"/>
       <c r="S26" s="5"/>
       <c r="T26" s="5">
@@ -7574,7 +7719,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W26" s="5"/>
+      <c r="W26" s="5">
+        <v>0</v>
+      </c>
       <c r="X26" s="1"/>
       <c r="Y26" s="5"/>
       <c r="Z26" s="5">
@@ -7621,7 +7768,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K27" s="5"/>
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
@@ -7636,7 +7785,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q27" s="5"/>
+      <c r="Q27" s="5">
+        <v>0</v>
+      </c>
       <c r="R27" s="1"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
@@ -7651,7 +7802,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W27" s="5"/>
+      <c r="W27" s="5">
+        <v>0</v>
+      </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5">
@@ -7698,7 +7851,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K28" s="5"/>
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
       <c r="L28" s="1"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
@@ -7713,7 +7868,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q28" s="5"/>
+      <c r="Q28" s="5">
+        <v>0</v>
+      </c>
       <c r="R28" s="1"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5">
@@ -7728,7 +7885,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W28" s="5"/>
+      <c r="W28" s="5">
+        <v>0</v>
+      </c>
       <c r="X28" s="1"/>
       <c r="Y28" s="5"/>
       <c r="Z28" s="5">
@@ -7775,7 +7934,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K29" s="5"/>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
@@ -7790,7 +7951,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q29" s="5"/>
+      <c r="Q29" s="5">
+        <v>0</v>
+      </c>
       <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
@@ -7805,7 +7968,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W29" s="5"/>
+      <c r="W29" s="5">
+        <v>0</v>
+      </c>
       <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
@@ -7852,7 +8017,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K30" s="5"/>
+      <c r="K30" s="5">
+        <v>0</v>
+      </c>
       <c r="L30" s="1"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5">
@@ -7867,7 +8034,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q30" s="5"/>
+      <c r="Q30" s="5">
+        <v>0</v>
+      </c>
       <c r="R30" s="1"/>
       <c r="S30" s="5"/>
       <c r="T30" s="5">
@@ -7882,7 +8051,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W30" s="5"/>
+      <c r="W30" s="5">
+        <v>0</v>
+      </c>
       <c r="X30" s="1"/>
       <c r="Y30" s="5"/>
       <c r="Z30" s="5">
@@ -7908,7 +8079,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="5">
+        <v>0</v>
+      </c>
       <c r="F31" s="1"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
@@ -7923,7 +8096,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K31" s="5"/>
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
       <c r="L31" s="1"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5">
@@ -7938,7 +8113,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q31" s="5"/>
+      <c r="Q31" s="5">
+        <v>0</v>
+      </c>
       <c r="R31" s="1"/>
       <c r="S31" s="5"/>
       <c r="T31" s="5">
@@ -7953,7 +8130,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W31" s="5"/>
+      <c r="W31" s="5">
+        <v>0</v>
+      </c>
       <c r="X31" s="1"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5">
@@ -8010,7 +8189,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K33" s="5"/>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
       <c r="L33" s="1"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5">
@@ -8025,7 +8206,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q33" s="5"/>
+      <c r="Q33" s="5">
+        <v>0</v>
+      </c>
       <c r="R33" s="1"/>
       <c r="S33" s="5"/>
       <c r="T33" s="5">
@@ -8040,7 +8223,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W33" s="5"/>
+      <c r="W33" s="5">
+        <v>0</v>
+      </c>
       <c r="X33" s="1"/>
       <c r="Y33" s="5"/>
       <c r="Z33" s="5">
@@ -8083,7 +8268,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K34" s="5"/>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
       <c r="L34" s="1"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5">
@@ -8098,7 +8285,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q34" s="5"/>
+      <c r="Q34" s="5">
+        <v>0</v>
+      </c>
       <c r="R34" s="1"/>
       <c r="S34" s="5"/>
       <c r="T34" s="5">
@@ -8113,7 +8302,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W34" s="5"/>
+      <c r="W34" s="5">
+        <v>0</v>
+      </c>
       <c r="X34" s="1"/>
       <c r="Y34" s="5"/>
       <c r="Z34" s="5">
@@ -8156,7 +8347,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K35" s="5"/>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
       <c r="L35" s="1"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5">
@@ -8171,7 +8364,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q35" s="5"/>
+      <c r="Q35" s="5">
+        <v>0</v>
+      </c>
       <c r="R35" s="1"/>
       <c r="S35" s="5"/>
       <c r="T35" s="5">
@@ -8186,7 +8381,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W35" s="5"/>
+      <c r="W35" s="5">
+        <v>0</v>
+      </c>
       <c r="X35" s="1"/>
       <c r="Y35" s="5"/>
       <c r="Z35" s="5">
@@ -8229,7 +8426,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K36" s="5"/>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
       <c r="L36" s="1"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5">
@@ -8244,7 +8443,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q36" s="5"/>
+      <c r="Q36" s="5">
+        <v>0</v>
+      </c>
       <c r="R36" s="1"/>
       <c r="S36" s="5"/>
       <c r="T36" s="5">
@@ -8259,7 +8460,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W36" s="5"/>
+      <c r="W36" s="5">
+        <v>0</v>
+      </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="5"/>
       <c r="Z36" s="5">
@@ -8302,7 +8505,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K37" s="5"/>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
       <c r="L37" s="1"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5">
@@ -8317,7 +8522,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q37" s="5"/>
+      <c r="Q37" s="5">
+        <v>0</v>
+      </c>
       <c r="R37" s="1"/>
       <c r="S37" s="5"/>
       <c r="T37" s="5">
@@ -8332,7 +8539,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W37" s="5"/>
+      <c r="W37" s="5">
+        <v>0</v>
+      </c>
       <c r="X37" s="1"/>
       <c r="Y37" s="5"/>
       <c r="Z37" s="5">
@@ -8375,7 +8584,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K38" s="5"/>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
       <c r="L38" s="1"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5">
@@ -8390,7 +8601,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q38" s="5"/>
+      <c r="Q38" s="5">
+        <v>0</v>
+      </c>
       <c r="R38" s="1"/>
       <c r="S38" s="5"/>
       <c r="T38" s="5">
@@ -8405,7 +8618,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W38" s="5"/>
+      <c r="W38" s="5">
+        <v>0</v>
+      </c>
       <c r="X38" s="1"/>
       <c r="Y38" s="5"/>
       <c r="Z38" s="5">
@@ -8448,7 +8663,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K39" s="5"/>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
       <c r="L39" s="1"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5">
@@ -8463,7 +8680,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q39" s="5"/>
+      <c r="Q39" s="5">
+        <v>0</v>
+      </c>
       <c r="R39" s="1"/>
       <c r="S39" s="5"/>
       <c r="T39" s="5">
@@ -8478,7 +8697,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W39" s="5"/>
+      <c r="W39" s="5">
+        <v>0</v>
+      </c>
       <c r="X39" s="1"/>
       <c r="Y39" s="5"/>
       <c r="Z39" s="5">
@@ -8521,7 +8742,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K40" s="5"/>
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
       <c r="L40" s="1"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5">
@@ -8536,7 +8759,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q40" s="5"/>
+      <c r="Q40" s="5">
+        <v>0</v>
+      </c>
       <c r="R40" s="1"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5">
@@ -8551,7 +8776,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W40" s="5"/>
+      <c r="W40" s="5">
+        <v>0</v>
+      </c>
       <c r="X40" s="1"/>
       <c r="Y40" s="5"/>
       <c r="Z40" s="5">
@@ -8594,7 +8821,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K41" s="5"/>
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
       <c r="L41" s="1"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5">
@@ -8609,12 +8838,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="5"/>
+      <c r="Q41" s="5">
+        <v>434</v>
+      </c>
+      <c r="R41" s="1">
+        <v>2025</v>
+      </c>
+      <c r="S41" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="T41" s="5">
         <f t="shared" si="12"/>
-        <v>3048</v>
+        <v>2614</v>
       </c>
       <c r="U41" s="5">
         <f t="shared" si="13"/>
@@ -8625,17 +8860,13 @@
         <v>3048</v>
       </c>
       <c r="W41" s="5">
-        <v>434</v>
-      </c>
-      <c r="X41" s="1">
-        <v>2025</v>
-      </c>
-      <c r="Y41" s="5" t="s">
-        <v>62</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="5"/>
       <c r="Z41" s="5">
         <f t="shared" si="14"/>
-        <v>2614</v>
+        <v>3048</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="15"/>
@@ -8691,7 +8922,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K43" s="5"/>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
       <c r="L43" s="1"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5">
@@ -8706,7 +8939,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q43" s="5"/>
+      <c r="Q43" s="5">
+        <v>0</v>
+      </c>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
@@ -8721,7 +8956,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W43" s="5"/>
+      <c r="W43" s="5">
+        <v>0</v>
+      </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
@@ -8768,7 +9005,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K44" s="5"/>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
       <c r="L44" s="1"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5">
@@ -8783,7 +9022,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q44" s="5"/>
+      <c r="Q44" s="5">
+        <v>0</v>
+      </c>
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
@@ -8798,7 +9039,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W44" s="5"/>
+      <c r="W44" s="5">
+        <v>0</v>
+      </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
@@ -8845,7 +9088,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K45" s="5"/>
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
       <c r="L45" s="1"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5">
@@ -8860,7 +9105,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q45" s="5"/>
+      <c r="Q45" s="5">
+        <v>0</v>
+      </c>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
@@ -8875,7 +9122,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W45" s="5"/>
+      <c r="W45" s="5">
+        <v>0</v>
+      </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
@@ -8922,7 +9171,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K46" s="5"/>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
       <c r="L46" s="1"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
@@ -8937,7 +9188,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q46" s="5"/>
+      <c r="Q46" s="5">
+        <v>0</v>
+      </c>
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
@@ -8952,7 +9205,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W46" s="5"/>
+      <c r="W46" s="5">
+        <v>0</v>
+      </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
@@ -8999,7 +9254,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K47" s="5"/>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
       <c r="L47" s="1"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
@@ -9014,7 +9271,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q47" s="5"/>
+      <c r="Q47" s="5">
+        <v>0</v>
+      </c>
       <c r="R47" s="1"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5">
@@ -9029,7 +9288,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W47" s="5"/>
+      <c r="W47" s="5">
+        <v>0</v>
+      </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5">
@@ -9076,7 +9337,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K48" s="5"/>
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
       <c r="L48" s="1"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
@@ -9091,7 +9354,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q48" s="5"/>
+      <c r="Q48" s="5">
+        <v>0</v>
+      </c>
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
@@ -9106,7 +9371,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W48" s="5"/>
+      <c r="W48" s="5">
+        <v>0</v>
+      </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
@@ -9153,7 +9420,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K49" s="5"/>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
       <c r="L49" s="1"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5">
@@ -9168,7 +9437,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q49" s="5"/>
+      <c r="Q49" s="5">
+        <v>0</v>
+      </c>
       <c r="R49" s="1"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
@@ -9183,7 +9454,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W49" s="5"/>
+      <c r="W49" s="5">
+        <v>0</v>
+      </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5">
@@ -9230,7 +9503,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K50" s="5"/>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
       <c r="L50" s="1"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
@@ -9245,7 +9520,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q50" s="5"/>
+      <c r="Q50" s="5">
+        <v>0</v>
+      </c>
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
@@ -9260,7 +9537,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W50" s="5"/>
+      <c r="W50" s="5">
+        <v>0</v>
+      </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
@@ -9307,7 +9586,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K51" s="5"/>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
       <c r="L51" s="1"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
@@ -9322,7 +9603,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q51" s="5"/>
+      <c r="Q51" s="5">
+        <v>0</v>
+      </c>
       <c r="R51" s="1"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5">
@@ -9337,7 +9620,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W51" s="5"/>
+      <c r="W51" s="5">
+        <v>0</v>
+      </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5">
@@ -9394,7 +9679,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K53" s="5"/>
+      <c r="K53" s="5">
+        <v>0</v>
+      </c>
       <c r="L53" s="1"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
@@ -9409,7 +9696,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="Q53" s="5"/>
+      <c r="Q53" s="5">
+        <v>0</v>
+      </c>
       <c r="R53" s="1"/>
       <c r="S53" s="5"/>
       <c r="T53" s="5">
@@ -9424,7 +9713,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W53" s="5"/>
+      <c r="W53" s="5">
+        <v>0</v>
+      </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="5"/>
       <c r="Z53" s="5">
@@ -9467,7 +9758,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K54" s="5"/>
+      <c r="K54" s="5">
+        <v>0</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5">
@@ -9482,7 +9775,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="Q54" s="5"/>
+      <c r="Q54" s="5">
+        <v>0</v>
+      </c>
       <c r="R54" s="1"/>
       <c r="S54" s="5"/>
       <c r="T54" s="5">
@@ -9497,7 +9792,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W54" s="5"/>
+      <c r="W54" s="5">
+        <v>0</v>
+      </c>
       <c r="X54" s="1"/>
       <c r="Y54" s="5"/>
       <c r="Z54" s="5">
@@ -9540,7 +9837,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K55" s="5"/>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
       <c r="L55" s="1"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5">
@@ -9555,7 +9854,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="Q55" s="5"/>
+      <c r="Q55" s="5">
+        <v>0</v>
+      </c>
       <c r="R55" s="1"/>
       <c r="S55" s="5"/>
       <c r="T55" s="5">
@@ -9570,7 +9871,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W55" s="5"/>
+      <c r="W55" s="5">
+        <v>0</v>
+      </c>
       <c r="X55" s="1"/>
       <c r="Y55" s="5"/>
       <c r="Z55" s="5">
@@ -9613,7 +9916,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K56" s="5"/>
+      <c r="K56" s="5">
+        <v>0</v>
+      </c>
       <c r="L56" s="1"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5">
@@ -9628,7 +9933,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="Q56" s="5"/>
+      <c r="Q56" s="5">
+        <v>0</v>
+      </c>
       <c r="R56" s="1"/>
       <c r="S56" s="5"/>
       <c r="T56" s="5">
@@ -9643,7 +9950,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W56" s="5"/>
+      <c r="W56" s="5">
+        <v>0</v>
+      </c>
       <c r="X56" s="1"/>
       <c r="Y56" s="5"/>
       <c r="Z56" s="5">
@@ -9686,7 +9995,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K57" s="5"/>
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
       <c r="L57" s="1"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5">
@@ -9701,7 +10012,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="Q57" s="5"/>
+      <c r="Q57" s="5">
+        <v>0</v>
+      </c>
       <c r="R57" s="1"/>
       <c r="S57" s="5"/>
       <c r="T57" s="5">
@@ -9716,7 +10029,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W57" s="5"/>
+      <c r="W57" s="5">
+        <v>0</v>
+      </c>
       <c r="X57" s="1"/>
       <c r="Y57" s="5"/>
       <c r="Z57" s="5">
@@ -9759,7 +10074,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K58" s="5"/>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
@@ -9774,7 +10091,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="Q58" s="5"/>
+      <c r="Q58" s="5">
+        <v>0</v>
+      </c>
       <c r="R58" s="1"/>
       <c r="S58" s="5"/>
       <c r="T58" s="5">
@@ -9789,7 +10108,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W58" s="5"/>
+      <c r="W58" s="5">
+        <v>0</v>
+      </c>
       <c r="X58" s="1"/>
       <c r="Y58" s="5"/>
       <c r="Z58" s="5">
@@ -9832,7 +10153,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K59" s="5"/>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
       <c r="L59" s="1"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5">
@@ -9847,7 +10170,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="Q59" s="5"/>
+      <c r="Q59" s="5">
+        <v>0</v>
+      </c>
       <c r="R59" s="1"/>
       <c r="S59" s="5"/>
       <c r="T59" s="5">
@@ -9862,7 +10187,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W59" s="5"/>
+      <c r="W59" s="5">
+        <v>0</v>
+      </c>
       <c r="X59" s="1"/>
       <c r="Y59" s="5"/>
       <c r="Z59" s="5">
@@ -9905,7 +10232,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K60" s="5"/>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
       <c r="L60" s="1"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5">
@@ -9920,7 +10249,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="Q60" s="5"/>
+      <c r="Q60" s="5">
+        <v>0</v>
+      </c>
       <c r="R60" s="1"/>
       <c r="S60" s="5"/>
       <c r="T60" s="5">
@@ -9935,7 +10266,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W60" s="5"/>
+      <c r="W60" s="5">
+        <v>0</v>
+      </c>
       <c r="X60" s="1"/>
       <c r="Y60" s="5"/>
       <c r="Z60" s="5">
@@ -9961,7 +10294,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="5">
+        <v>0</v>
+      </c>
       <c r="F61" s="1"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5">
@@ -9976,7 +10311,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K61" s="5"/>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
       <c r="L61" s="1"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5">
@@ -9991,7 +10328,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="Q61" s="5"/>
+      <c r="Q61" s="5">
+        <v>0</v>
+      </c>
       <c r="R61" s="1"/>
       <c r="S61" s="5"/>
       <c r="T61" s="5">
@@ -10006,7 +10345,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W61" s="5"/>
+      <c r="W61" s="5">
+        <v>0</v>
+      </c>
       <c r="X61" s="1"/>
       <c r="Y61" s="5"/>
       <c r="Z61" s="5">
@@ -10063,7 +10404,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K63" s="12"/>
+      <c r="K63" s="12">
+        <v>0</v>
+      </c>
       <c r="L63" s="10"/>
       <c r="M63" s="12"/>
       <c r="N63" s="12">
@@ -10093,7 +10436,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W63" s="12"/>
+      <c r="W63" s="12">
+        <v>0</v>
+      </c>
       <c r="X63" s="10"/>
       <c r="Y63" s="12"/>
       <c r="Z63" s="12">
@@ -10136,7 +10481,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K64" s="12"/>
+      <c r="K64" s="12">
+        <v>0</v>
+      </c>
       <c r="L64" s="10"/>
       <c r="M64" s="12"/>
       <c r="N64" s="12">
@@ -10166,7 +10513,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W64" s="12"/>
+      <c r="W64" s="12">
+        <v>0</v>
+      </c>
       <c r="X64" s="10"/>
       <c r="Y64" s="12"/>
       <c r="Z64" s="12">
@@ -10209,7 +10558,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K65" s="12"/>
+      <c r="K65" s="12">
+        <v>0</v>
+      </c>
       <c r="L65" s="10"/>
       <c r="M65" s="12"/>
       <c r="N65" s="12">
@@ -10239,7 +10590,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W65" s="12"/>
+      <c r="W65" s="12">
+        <v>0</v>
+      </c>
       <c r="X65" s="10"/>
       <c r="Y65" s="12"/>
       <c r="Z65" s="12">
@@ -10282,7 +10635,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K66" s="12"/>
+      <c r="K66" s="12">
+        <v>0</v>
+      </c>
       <c r="L66" s="10"/>
       <c r="M66" s="12"/>
       <c r="N66" s="12">
@@ -10312,7 +10667,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W66" s="12"/>
+      <c r="W66" s="12">
+        <v>0</v>
+      </c>
       <c r="X66" s="10"/>
       <c r="Y66" s="12"/>
       <c r="Z66" s="12">
@@ -10355,7 +10712,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K67" s="12"/>
+      <c r="K67" s="12">
+        <v>0</v>
+      </c>
       <c r="L67" s="10"/>
       <c r="M67" s="12"/>
       <c r="N67" s="12">
@@ -10385,7 +10744,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W67" s="12"/>
+      <c r="W67" s="12">
+        <v>0</v>
+      </c>
       <c r="X67" s="10"/>
       <c r="Y67" s="12"/>
       <c r="Z67" s="12">
@@ -10428,7 +10789,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K68" s="12"/>
+      <c r="K68" s="12">
+        <v>0</v>
+      </c>
       <c r="L68" s="10"/>
       <c r="M68" s="12"/>
       <c r="N68" s="12">
@@ -10458,7 +10821,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W68" s="12"/>
+      <c r="W68" s="12">
+        <v>0</v>
+      </c>
       <c r="X68" s="10"/>
       <c r="Y68" s="12"/>
       <c r="Z68" s="12">
@@ -10501,7 +10866,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K69" s="12"/>
+      <c r="K69" s="12">
+        <v>0</v>
+      </c>
       <c r="L69" s="10"/>
       <c r="M69" s="12"/>
       <c r="N69" s="12">
@@ -10531,7 +10898,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W69" s="12"/>
+      <c r="W69" s="12">
+        <v>0</v>
+      </c>
       <c r="X69" s="10"/>
       <c r="Y69" s="12"/>
       <c r="Z69" s="12">
@@ -10574,7 +10943,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K70" s="12"/>
+      <c r="K70" s="12">
+        <v>0</v>
+      </c>
       <c r="L70" s="10"/>
       <c r="M70" s="12"/>
       <c r="N70" s="12">
@@ -10604,7 +10975,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W70" s="12"/>
+      <c r="W70" s="12">
+        <v>0</v>
+      </c>
       <c r="X70" s="10"/>
       <c r="Y70" s="12"/>
       <c r="Z70" s="12">
@@ -10647,7 +11020,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K71" s="12"/>
+      <c r="K71" s="12">
+        <v>0</v>
+      </c>
       <c r="L71" s="10"/>
       <c r="M71" s="12"/>
       <c r="N71" s="12">
@@ -10677,7 +11052,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W71" s="12"/>
+      <c r="W71" s="12">
+        <v>0</v>
+      </c>
       <c r="X71" s="10"/>
       <c r="Y71" s="12"/>
       <c r="Z71" s="12">
@@ -10734,7 +11111,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K73" s="12"/>
+      <c r="K73" s="12">
+        <v>0</v>
+      </c>
       <c r="L73" s="10"/>
       <c r="M73" s="12"/>
       <c r="N73" s="12">
@@ -10764,7 +11143,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W73" s="12"/>
+      <c r="W73" s="12">
+        <v>0</v>
+      </c>
       <c r="X73" s="10"/>
       <c r="Y73" s="12"/>
       <c r="Z73" s="12">
@@ -10807,7 +11188,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K74" s="12"/>
+      <c r="K74" s="12">
+        <v>0</v>
+      </c>
       <c r="L74" s="10"/>
       <c r="M74" s="12"/>
       <c r="N74" s="12">
@@ -10837,7 +11220,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W74" s="12"/>
+      <c r="W74" s="12">
+        <v>0</v>
+      </c>
       <c r="X74" s="10"/>
       <c r="Y74" s="12"/>
       <c r="Z74" s="12">
@@ -10880,7 +11265,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K75" s="12"/>
+      <c r="K75" s="12">
+        <v>0</v>
+      </c>
       <c r="L75" s="10"/>
       <c r="M75" s="12"/>
       <c r="N75" s="12">
@@ -10910,7 +11297,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W75" s="12"/>
+      <c r="W75" s="12">
+        <v>0</v>
+      </c>
       <c r="X75" s="10"/>
       <c r="Y75" s="12"/>
       <c r="Z75" s="12">
@@ -10953,7 +11342,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K76" s="12"/>
+      <c r="K76" s="12">
+        <v>0</v>
+      </c>
       <c r="L76" s="10"/>
       <c r="M76" s="12"/>
       <c r="N76" s="12">
@@ -10983,7 +11374,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W76" s="12"/>
+      <c r="W76" s="12">
+        <v>0</v>
+      </c>
       <c r="X76" s="10"/>
       <c r="Y76" s="12"/>
       <c r="Z76" s="12">
@@ -11026,7 +11419,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K77" s="12"/>
+      <c r="K77" s="12">
+        <v>0</v>
+      </c>
       <c r="L77" s="10"/>
       <c r="M77" s="12"/>
       <c r="N77" s="12">
@@ -11056,7 +11451,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W77" s="12"/>
+      <c r="W77" s="12">
+        <v>0</v>
+      </c>
       <c r="X77" s="10"/>
       <c r="Y77" s="12"/>
       <c r="Z77" s="12">
@@ -11099,7 +11496,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K78" s="12"/>
+      <c r="K78" s="12">
+        <v>0</v>
+      </c>
       <c r="L78" s="10"/>
       <c r="M78" s="12"/>
       <c r="N78" s="12">
@@ -11129,7 +11528,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W78" s="12"/>
+      <c r="W78" s="12">
+        <v>0</v>
+      </c>
       <c r="X78" s="10"/>
       <c r="Y78" s="12"/>
       <c r="Z78" s="12">
@@ -11172,7 +11573,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K79" s="12"/>
+      <c r="K79" s="12">
+        <v>0</v>
+      </c>
       <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
@@ -11202,7 +11605,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W79" s="12"/>
+      <c r="W79" s="12">
+        <v>0</v>
+      </c>
       <c r="X79" s="10"/>
       <c r="Y79" s="12"/>
       <c r="Z79" s="12">
@@ -11245,7 +11650,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K80" s="12"/>
+      <c r="K80" s="12">
+        <v>0</v>
+      </c>
       <c r="L80" s="10"/>
       <c r="M80" s="12"/>
       <c r="N80" s="12">
@@ -11275,7 +11682,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W80" s="12"/>
+      <c r="W80" s="12">
+        <v>0</v>
+      </c>
       <c r="X80" s="10"/>
       <c r="Y80" s="12"/>
       <c r="Z80" s="12">
@@ -11318,7 +11727,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K81" s="12"/>
+      <c r="K81" s="12">
+        <v>0</v>
+      </c>
       <c r="L81" s="10"/>
       <c r="M81" s="12"/>
       <c r="N81" s="12">
@@ -11348,7 +11759,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W81" s="12"/>
+      <c r="W81" s="12">
+        <v>0</v>
+      </c>
       <c r="X81" s="10"/>
       <c r="Y81" s="12"/>
       <c r="Z81" s="12">
@@ -11405,7 +11818,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K83" s="12"/>
+      <c r="K83" s="12">
+        <v>0</v>
+      </c>
       <c r="L83" s="10"/>
       <c r="M83" s="12"/>
       <c r="N83" s="12">
@@ -11435,7 +11850,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="W83" s="12"/>
+      <c r="W83" s="12">
+        <v>0</v>
+      </c>
       <c r="X83" s="10"/>
       <c r="Y83" s="12"/>
       <c r="Z83" s="12">
@@ -11478,7 +11895,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K84" s="12"/>
+      <c r="K84" s="12">
+        <v>0</v>
+      </c>
       <c r="L84" s="10"/>
       <c r="M84" s="12"/>
       <c r="N84" s="12">
@@ -11508,7 +11927,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="W84" s="12"/>
+      <c r="W84" s="12">
+        <v>0</v>
+      </c>
       <c r="X84" s="10"/>
       <c r="Y84" s="12"/>
       <c r="Z84" s="12">
@@ -11551,7 +11972,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K85" s="12"/>
+      <c r="K85" s="12">
+        <v>0</v>
+      </c>
       <c r="L85" s="10"/>
       <c r="M85" s="12"/>
       <c r="N85" s="12">
@@ -11581,7 +12004,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="W85" s="12"/>
+      <c r="W85" s="12">
+        <v>0</v>
+      </c>
       <c r="X85" s="10"/>
       <c r="Y85" s="12"/>
       <c r="Z85" s="12">
@@ -11624,7 +12049,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K86" s="12"/>
+      <c r="K86" s="12">
+        <v>0</v>
+      </c>
       <c r="L86" s="10"/>
       <c r="M86" s="12"/>
       <c r="N86" s="12">
@@ -11654,7 +12081,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="W86" s="12"/>
+      <c r="W86" s="12">
+        <v>0</v>
+      </c>
       <c r="X86" s="10"/>
       <c r="Y86" s="12"/>
       <c r="Z86" s="12">
@@ -11697,7 +12126,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K87" s="12"/>
+      <c r="K87" s="12">
+        <v>0</v>
+      </c>
       <c r="L87" s="10"/>
       <c r="M87" s="12"/>
       <c r="N87" s="12">
@@ -11727,7 +12158,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="W87" s="12"/>
+      <c r="W87" s="12">
+        <v>0</v>
+      </c>
       <c r="X87" s="10"/>
       <c r="Y87" s="12"/>
       <c r="Z87" s="12">
@@ -11770,7 +12203,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K88" s="12"/>
+      <c r="K88" s="12">
+        <v>0</v>
+      </c>
       <c r="L88" s="10"/>
       <c r="M88" s="12"/>
       <c r="N88" s="12">
@@ -11800,7 +12235,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="W88" s="12"/>
+      <c r="W88" s="12">
+        <v>0</v>
+      </c>
       <c r="X88" s="10"/>
       <c r="Y88" s="12"/>
       <c r="Z88" s="12">
@@ -11843,7 +12280,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K89" s="12"/>
+      <c r="K89" s="12">
+        <v>0</v>
+      </c>
       <c r="L89" s="10"/>
       <c r="M89" s="12"/>
       <c r="N89" s="12">
@@ -11873,7 +12312,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="W89" s="12"/>
+      <c r="W89" s="12">
+        <v>0</v>
+      </c>
       <c r="X89" s="10"/>
       <c r="Y89" s="12"/>
       <c r="Z89" s="12">
@@ -11916,7 +12357,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K90" s="12"/>
+      <c r="K90" s="12">
+        <v>0</v>
+      </c>
       <c r="L90" s="10"/>
       <c r="M90" s="12"/>
       <c r="N90" s="12">
@@ -11946,7 +12389,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="W90" s="12"/>
+      <c r="W90" s="12">
+        <v>0</v>
+      </c>
       <c r="X90" s="10"/>
       <c r="Y90" s="12"/>
       <c r="Z90" s="12">
@@ -11989,7 +12434,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K91" s="12"/>
+      <c r="K91" s="12">
+        <v>0</v>
+      </c>
       <c r="L91" s="10"/>
       <c r="M91" s="12"/>
       <c r="N91" s="12">
@@ -12019,7 +12466,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="W91" s="12"/>
+      <c r="W91" s="12">
+        <v>0</v>
+      </c>
       <c r="X91" s="10"/>
       <c r="Y91" s="12"/>
       <c r="Z91" s="12">
@@ -12076,7 +12525,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="K93" s="12"/>
+      <c r="K93" s="12">
+        <v>0</v>
+      </c>
       <c r="L93" s="10"/>
       <c r="M93" s="12"/>
       <c r="N93" s="12">
@@ -12106,7 +12557,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="W93" s="12"/>
+      <c r="W93" s="12">
+        <v>0</v>
+      </c>
       <c r="X93" s="10"/>
       <c r="Y93" s="12"/>
       <c r="Z93" s="12">
@@ -12149,7 +12602,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="K94" s="12"/>
+      <c r="K94" s="12">
+        <v>0</v>
+      </c>
       <c r="L94" s="10"/>
       <c r="M94" s="12"/>
       <c r="N94" s="12">
@@ -12179,7 +12634,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="W94" s="12"/>
+      <c r="W94" s="12">
+        <v>0</v>
+      </c>
       <c r="X94" s="10"/>
       <c r="Y94" s="12"/>
       <c r="Z94" s="12">
@@ -12222,7 +12679,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="K95" s="12"/>
+      <c r="K95" s="12">
+        <v>0</v>
+      </c>
       <c r="L95" s="10"/>
       <c r="M95" s="12"/>
       <c r="N95" s="12">
@@ -12252,7 +12711,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="W95" s="12"/>
+      <c r="W95" s="12">
+        <v>0</v>
+      </c>
       <c r="X95" s="10"/>
       <c r="Y95" s="12"/>
       <c r="Z95" s="12">
@@ -12295,7 +12756,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="K96" s="12"/>
+      <c r="K96" s="12">
+        <v>0</v>
+      </c>
       <c r="L96" s="10"/>
       <c r="M96" s="12"/>
       <c r="N96" s="12">
@@ -12325,7 +12788,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="W96" s="12"/>
+      <c r="W96" s="12">
+        <v>0</v>
+      </c>
       <c r="X96" s="10"/>
       <c r="Y96" s="12"/>
       <c r="Z96" s="12">
@@ -12368,7 +12833,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="K97" s="12"/>
+      <c r="K97" s="12">
+        <v>0</v>
+      </c>
       <c r="L97" s="10"/>
       <c r="M97" s="12"/>
       <c r="N97" s="12">
@@ -12398,7 +12865,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="W97" s="12"/>
+      <c r="W97" s="12">
+        <v>0</v>
+      </c>
       <c r="X97" s="10"/>
       <c r="Y97" s="12"/>
       <c r="Z97" s="12">
@@ -12441,7 +12910,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="K98" s="12"/>
+      <c r="K98" s="12">
+        <v>0</v>
+      </c>
       <c r="L98" s="10"/>
       <c r="M98" s="12"/>
       <c r="N98" s="12">
@@ -12471,7 +12942,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="W98" s="12"/>
+      <c r="W98" s="12">
+        <v>0</v>
+      </c>
       <c r="X98" s="10"/>
       <c r="Y98" s="12"/>
       <c r="Z98" s="12">
@@ -12514,7 +12987,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="K99" s="12"/>
+      <c r="K99" s="12">
+        <v>0</v>
+      </c>
       <c r="L99" s="10"/>
       <c r="M99" s="12"/>
       <c r="N99" s="12">
@@ -12544,7 +13019,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="W99" s="12"/>
+      <c r="W99" s="12">
+        <v>0</v>
+      </c>
       <c r="X99" s="10"/>
       <c r="Y99" s="12"/>
       <c r="Z99" s="12">
@@ -12587,7 +13064,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="K100" s="12"/>
+      <c r="K100" s="12">
+        <v>0</v>
+      </c>
       <c r="L100" s="10"/>
       <c r="M100" s="12"/>
       <c r="N100" s="12">
@@ -12617,7 +13096,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="W100" s="12"/>
+      <c r="W100" s="12">
+        <v>0</v>
+      </c>
       <c r="X100" s="10"/>
       <c r="Y100" s="12"/>
       <c r="Z100" s="12">
@@ -12660,7 +13141,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="K101" s="12"/>
+      <c r="K101" s="12">
+        <v>0</v>
+      </c>
       <c r="L101" s="10"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12">
@@ -12690,7 +13173,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3200</v>
       </c>
-      <c r="W101" s="12"/>
+      <c r="W101" s="12">
+        <v>0</v>
+      </c>
       <c r="X101" s="10"/>
       <c r="Y101" s="12"/>
       <c r="Z101" s="12">
@@ -12747,7 +13232,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K103" s="5"/>
+      <c r="K103" s="5">
+        <v>0</v>
+      </c>
       <c r="L103" s="1"/>
       <c r="M103" s="5"/>
       <c r="N103" s="5">
@@ -12777,7 +13264,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W103" s="5"/>
+      <c r="W103" s="5">
+        <v>0</v>
+      </c>
       <c r="X103" s="1"/>
       <c r="Y103" s="5"/>
       <c r="Z103" s="5">
@@ -12820,7 +13309,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K104" s="5"/>
+      <c r="K104" s="5">
+        <v>0</v>
+      </c>
       <c r="L104" s="1"/>
       <c r="M104" s="5"/>
       <c r="N104" s="5">
@@ -12850,7 +13341,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W104" s="5"/>
+      <c r="W104" s="5">
+        <v>0</v>
+      </c>
       <c r="X104" s="1"/>
       <c r="Y104" s="5"/>
       <c r="Z104" s="5">
@@ -12893,7 +13386,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K105" s="5"/>
+      <c r="K105" s="5">
+        <v>0</v>
+      </c>
       <c r="L105" s="1"/>
       <c r="M105" s="5"/>
       <c r="N105" s="5">
@@ -12923,7 +13418,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W105" s="5"/>
+      <c r="W105" s="5">
+        <v>0</v>
+      </c>
       <c r="X105" s="1"/>
       <c r="Y105" s="5"/>
       <c r="Z105" s="5">
@@ -12966,7 +13463,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K106" s="5"/>
+      <c r="K106" s="5">
+        <v>0</v>
+      </c>
       <c r="L106" s="1"/>
       <c r="M106" s="5"/>
       <c r="N106" s="5">
@@ -12996,7 +13495,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W106" s="5"/>
+      <c r="W106" s="5">
+        <v>0</v>
+      </c>
       <c r="X106" s="1"/>
       <c r="Y106" s="5"/>
       <c r="Z106" s="5">
@@ -13039,7 +13540,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K107" s="5"/>
+      <c r="K107" s="5">
+        <v>0</v>
+      </c>
       <c r="L107" s="1"/>
       <c r="M107" s="5"/>
       <c r="N107" s="5">
@@ -13069,7 +13572,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W107" s="5"/>
+      <c r="W107" s="5">
+        <v>0</v>
+      </c>
       <c r="X107" s="1"/>
       <c r="Y107" s="5"/>
       <c r="Z107" s="5">
@@ -13112,7 +13617,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K108" s="5"/>
+      <c r="K108" s="5">
+        <v>0</v>
+      </c>
       <c r="L108" s="1"/>
       <c r="M108" s="5"/>
       <c r="N108" s="5">
@@ -13142,7 +13649,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W108" s="5"/>
+      <c r="W108" s="5">
+        <v>0</v>
+      </c>
       <c r="X108" s="1"/>
       <c r="Y108" s="5"/>
       <c r="Z108" s="5">
@@ -13185,7 +13694,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K109" s="5"/>
+      <c r="K109" s="5">
+        <v>0</v>
+      </c>
       <c r="L109" s="1"/>
       <c r="M109" s="5"/>
       <c r="N109" s="5">
@@ -13215,7 +13726,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W109" s="5"/>
+      <c r="W109" s="5">
+        <v>0</v>
+      </c>
       <c r="X109" s="1"/>
       <c r="Y109" s="5"/>
       <c r="Z109" s="5">
@@ -13258,7 +13771,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K110" s="5"/>
+      <c r="K110" s="5">
+        <v>0</v>
+      </c>
       <c r="L110" s="1"/>
       <c r="M110" s="5"/>
       <c r="N110" s="5">
@@ -13288,7 +13803,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W110" s="5"/>
+      <c r="W110" s="5">
+        <v>0</v>
+      </c>
       <c r="X110" s="1"/>
       <c r="Y110" s="5"/>
       <c r="Z110" s="5">
@@ -14300,190 +14817,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C112:C127" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F15 Q14:R21 W14:X21 D23:F24 Q23:R31 W23:X31 H33:I41 Q33:R41 W33:X41 H43:I51 Q43:R51 W43:X51 H53:I61 Q53:R61 W53:X61 H63:I71 Q63:R71 W63:X71 H73:I81 Q73:R81 W73:X81 H83:I91 Q83:R91 W83:X91 H93:I101 Q93:R101 W93:X101 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L15 K23:L31 Q112:R126 P2:R2 N13:P126 T13:V127 J6:J127 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 V2:X3 D21:F21 D16:E20 K21:L21 K16:K20 D31:F31 D25:E30 D5:F12 D33:F41 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110 D43:F51" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F15 D23:F24 H33:I41 H43:I51 H53:I61 H63:I71 Q63:R71 H73:I81 Q73:R81 H83:I91 Q83:R91 H93:I101 Q93:R101 H103:I110 Q103:R110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K112:L127 K14:L15 Q112:R126 P2:R2 N13:P126 T13:V127 J6:J127 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 V2:X3 D21:F21 D16:E20 K21:L21 K16:K20 D31:F31 D25:E30 D5:F12 D33:F41 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110 D43:F51 K6:L12 K23:L31 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 T5:X12 W14:X21 W23:X31 W33:X41 W43:X51 W53:X61 W63:X71 W73:X81 W83:X91 W93:X101 W103:X110" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G15 M14:M15 M3 Y14:Y110 G23:G24 G33:G41 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 Y2:AA3 G21 M21:M110 G31 G43:G51" name="SOURCE"/>
     <protectedRange sqref="C5:C12" name="Textbooks_1"/>
     <protectedRange sqref="C14:C21" name="Textbooks_2"/>
@@ -14506,15 +14843,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 F14:F21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 L14:L21 F33:F41 F23:F31 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 X3 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127 F43:F51" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G14:G21 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 Y3 M14:M110 G33:G41 G23:G31 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 G43:G51" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110 X112:X127" xr:uid="{E996C1C8-7900-49CC-A2DA-57D45A3C61FD}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14530,7 +14870,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14707,22 +15047,26 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K3" s="5"/>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5">
-        <f t="shared" ref="N3:N72" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
+        <f t="shared" ref="N3:N60" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
         <v>2648</v>
       </c>
       <c r="O3" s="5">
-        <f t="shared" ref="O3:O72" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
+        <f t="shared" ref="O3:O60" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
         <v>0</v>
       </c>
       <c r="P3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q3" s="5"/>
+      <c r="Q3" s="5">
+        <v>0</v>
+      </c>
       <c r="R3" s="1"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5">
@@ -14737,7 +15081,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W3" s="5"/>
+      <c r="W3" s="5">
+        <v>0</v>
+      </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5">
@@ -14780,7 +15126,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5">
@@ -14795,7 +15143,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q4" s="5"/>
+      <c r="Q4" s="5">
+        <v>0</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="5"/>
       <c r="T4" s="5">
@@ -14810,7 +15160,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W4" s="5"/>
+      <c r="W4" s="5">
+        <v>0</v>
+      </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="5"/>
       <c r="Z4" s="5">
@@ -14853,7 +15205,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K5" s="5"/>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
@@ -14868,7 +15222,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q5" s="5"/>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
@@ -14883,7 +15239,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W5" s="5"/>
+      <c r="W5" s="5">
+        <v>0</v>
+      </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
@@ -14926,7 +15284,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K6" s="5"/>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
@@ -14941,7 +15301,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q6" s="5"/>
+      <c r="Q6" s="5">
+        <v>0</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
@@ -14956,7 +15318,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W6" s="5"/>
+      <c r="W6" s="5">
+        <v>0</v>
+      </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
@@ -14999,7 +15363,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K7" s="5"/>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
@@ -15014,7 +15380,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q7" s="5"/>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
@@ -15029,7 +15397,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W7" s="5"/>
+      <c r="W7" s="5">
+        <v>0</v>
+      </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
@@ -15072,7 +15442,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K8" s="5"/>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
@@ -15087,7 +15459,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q8" s="5"/>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
@@ -15102,7 +15476,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W8" s="5"/>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
@@ -15145,7 +15521,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K9" s="5"/>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
@@ -15160,7 +15538,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q9" s="5"/>
+      <c r="Q9" s="5">
+        <v>0</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
@@ -15175,7 +15555,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W9" s="5"/>
+      <c r="W9" s="5">
+        <v>0</v>
+      </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
@@ -15218,7 +15600,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="K10" s="5"/>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
@@ -15233,7 +15617,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="Q10" s="5"/>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
@@ -15248,7 +15634,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2648</v>
       </c>
-      <c r="W10" s="5"/>
+      <c r="W10" s="5">
+        <v>0</v>
+      </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
@@ -15292,7 +15680,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="K12" s="5"/>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
@@ -15307,7 +15697,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q12" s="5"/>
+      <c r="Q12" s="5">
+        <v>0</v>
+      </c>
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
@@ -15322,7 +15714,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W12" s="5"/>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
@@ -15365,7 +15759,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="K13" s="5"/>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
       <c r="L13" s="1"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5">
@@ -15380,7 +15776,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q13" s="5"/>
+      <c r="Q13" s="5">
+        <v>0</v>
+      </c>
       <c r="R13" s="1"/>
       <c r="S13" s="5"/>
       <c r="T13" s="5">
@@ -15395,7 +15793,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W13" s="5"/>
+      <c r="W13" s="5">
+        <v>0</v>
+      </c>
       <c r="X13" s="1"/>
       <c r="Y13" s="5"/>
       <c r="Z13" s="5">
@@ -15438,7 +15838,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="K14" s="5"/>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5">
@@ -15453,7 +15855,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q14" s="5"/>
+      <c r="Q14" s="5">
+        <v>0</v>
+      </c>
       <c r="R14" s="1"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
@@ -15468,7 +15872,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W14" s="5"/>
+      <c r="W14" s="5">
+        <v>0</v>
+      </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
@@ -15511,7 +15917,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="K15" s="5"/>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5">
@@ -15526,7 +15934,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q15" s="5"/>
+      <c r="Q15" s="5">
+        <v>0</v>
+      </c>
       <c r="R15" s="1"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
@@ -15541,7 +15951,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W15" s="5"/>
+      <c r="W15" s="5">
+        <v>0</v>
+      </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
@@ -15584,7 +15996,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="K16" s="5"/>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5">
@@ -15599,7 +16013,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q16" s="5"/>
+      <c r="Q16" s="5">
+        <v>0</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5">
@@ -15663,7 +16079,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="K17" s="5"/>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
       <c r="L17" s="1"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5">
@@ -15678,7 +16096,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q17" s="5"/>
+      <c r="Q17" s="5">
+        <v>0</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
@@ -15742,7 +16162,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="K18" s="5"/>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
       <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
@@ -15757,7 +16179,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q18" s="5"/>
+      <c r="Q18" s="5">
+        <v>0</v>
+      </c>
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
@@ -15821,7 +16245,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="K19" s="5"/>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
@@ -15836,7 +16262,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="Q19" s="5"/>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
@@ -15851,7 +16279,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2816</v>
       </c>
-      <c r="W19" s="5"/>
+      <c r="W19" s="5">
+        <v>0</v>
+      </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
@@ -15895,7 +16325,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K21" s="5"/>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
       <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
@@ -15910,7 +16342,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q21" s="5"/>
+      <c r="Q21" s="5">
+        <v>0</v>
+      </c>
       <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
@@ -15925,7 +16359,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W21" s="5"/>
+      <c r="W21" s="5">
+        <v>0</v>
+      </c>
       <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
@@ -15968,7 +16404,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K22" s="5"/>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
       <c r="L22" s="1"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5">
@@ -15983,7 +16421,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q22" s="5"/>
+      <c r="Q22" s="5">
+        <v>0</v>
+      </c>
       <c r="R22" s="1"/>
       <c r="S22" s="5"/>
       <c r="T22" s="5">
@@ -15998,7 +16438,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W22" s="5"/>
+      <c r="W22" s="5">
+        <v>0</v>
+      </c>
       <c r="X22" s="1"/>
       <c r="Y22" s="5"/>
       <c r="Z22" s="5">
@@ -16041,7 +16483,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K23" s="5"/>
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5">
@@ -16056,7 +16500,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q23" s="5"/>
+      <c r="Q23" s="5">
+        <v>0</v>
+      </c>
       <c r="R23" s="1"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
@@ -16071,7 +16517,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W23" s="5"/>
+      <c r="W23" s="5">
+        <v>0</v>
+      </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5">
@@ -16114,7 +16562,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K24" s="5"/>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
       <c r="L24" s="1"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5">
@@ -16129,7 +16579,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q24" s="5"/>
+      <c r="Q24" s="5">
+        <v>0</v>
+      </c>
       <c r="R24" s="1"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5">
@@ -16144,7 +16596,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W24" s="5"/>
+      <c r="W24" s="5">
+        <v>0</v>
+      </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5">
@@ -16187,7 +16641,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K25" s="5"/>
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5">
@@ -16202,7 +16658,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q25" s="5"/>
+      <c r="Q25" s="5">
+        <v>0</v>
+      </c>
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
@@ -16217,7 +16675,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W25" s="5"/>
+      <c r="W25" s="5">
+        <v>0</v>
+      </c>
       <c r="X25" s="1"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
@@ -16260,7 +16720,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K26" s="5"/>
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5">
@@ -16275,7 +16737,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q26" s="5"/>
+      <c r="Q26" s="5">
+        <v>0</v>
+      </c>
       <c r="R26" s="1"/>
       <c r="S26" s="5"/>
       <c r="T26" s="5">
@@ -16339,7 +16803,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K27" s="5"/>
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
@@ -16354,7 +16820,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q27" s="5"/>
+      <c r="Q27" s="5">
+        <v>0</v>
+      </c>
       <c r="R27" s="1"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
@@ -16418,7 +16886,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K28" s="5"/>
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
       <c r="L28" s="1"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
@@ -16433,7 +16903,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q28" s="5"/>
+      <c r="Q28" s="5">
+        <v>0</v>
+      </c>
       <c r="R28" s="1"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5">
@@ -16497,7 +16969,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="K29" s="5"/>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
@@ -16512,7 +16986,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="Q29" s="5"/>
+      <c r="Q29" s="5">
+        <v>0</v>
+      </c>
       <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
@@ -16527,7 +17003,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3096</v>
       </c>
-      <c r="W29" s="5"/>
+      <c r="W29" s="5">
+        <v>0</v>
+      </c>
       <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
@@ -16571,7 +17049,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K31" s="5"/>
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
       <c r="L31" s="1"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5">
@@ -16586,7 +17066,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q31" s="5"/>
+      <c r="Q31" s="5">
+        <v>0</v>
+      </c>
       <c r="R31" s="1"/>
       <c r="S31" s="5"/>
       <c r="T31" s="5">
@@ -16601,7 +17083,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W31" s="5"/>
+      <c r="W31" s="5">
+        <v>0</v>
+      </c>
       <c r="X31" s="1"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5">
@@ -16644,7 +17128,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K32" s="5"/>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
       <c r="L32" s="1"/>
       <c r="M32" s="5"/>
       <c r="N32" s="5">
@@ -16659,7 +17145,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q32" s="5"/>
+      <c r="Q32" s="5">
+        <v>0</v>
+      </c>
       <c r="R32" s="1"/>
       <c r="S32" s="5"/>
       <c r="T32" s="5">
@@ -16674,7 +17162,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W32" s="5"/>
+      <c r="W32" s="5">
+        <v>0</v>
+      </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="5"/>
       <c r="Z32" s="5">
@@ -16717,7 +17207,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K33" s="5"/>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
       <c r="L33" s="1"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5">
@@ -16732,7 +17224,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q33" s="5"/>
+      <c r="Q33" s="5">
+        <v>0</v>
+      </c>
       <c r="R33" s="1"/>
       <c r="S33" s="5"/>
       <c r="T33" s="5">
@@ -16747,7 +17241,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W33" s="5"/>
+      <c r="W33" s="5">
+        <v>0</v>
+      </c>
       <c r="X33" s="1"/>
       <c r="Y33" s="5"/>
       <c r="Z33" s="5">
@@ -16790,7 +17286,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K34" s="5"/>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
       <c r="L34" s="1"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5">
@@ -16805,7 +17303,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q34" s="5"/>
+      <c r="Q34" s="5">
+        <v>0</v>
+      </c>
       <c r="R34" s="1"/>
       <c r="S34" s="5"/>
       <c r="T34" s="5">
@@ -16820,7 +17320,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W34" s="5"/>
+      <c r="W34" s="5">
+        <v>0</v>
+      </c>
       <c r="X34" s="1"/>
       <c r="Y34" s="5"/>
       <c r="Z34" s="5">
@@ -16863,7 +17365,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K35" s="5"/>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
       <c r="L35" s="1"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5">
@@ -16878,7 +17382,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q35" s="5"/>
+      <c r="Q35" s="5">
+        <v>0</v>
+      </c>
       <c r="R35" s="1"/>
       <c r="S35" s="5"/>
       <c r="T35" s="5">
@@ -16893,7 +17399,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W35" s="5"/>
+      <c r="W35" s="5">
+        <v>0</v>
+      </c>
       <c r="X35" s="1"/>
       <c r="Y35" s="5"/>
       <c r="Z35" s="5">
@@ -16936,7 +17444,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K36" s="5"/>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
       <c r="L36" s="1"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5">
@@ -16951,7 +17461,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q36" s="5"/>
+      <c r="Q36" s="5">
+        <v>0</v>
+      </c>
       <c r="R36" s="1"/>
       <c r="S36" s="5"/>
       <c r="T36" s="5">
@@ -16966,7 +17478,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W36" s="5"/>
+      <c r="W36" s="5">
+        <v>0</v>
+      </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="5"/>
       <c r="Z36" s="5">
@@ -17009,7 +17523,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K37" s="5"/>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
       <c r="L37" s="1"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5">
@@ -17024,7 +17540,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q37" s="5"/>
+      <c r="Q37" s="5">
+        <v>0</v>
+      </c>
       <c r="R37" s="1"/>
       <c r="S37" s="5"/>
       <c r="T37" s="5">
@@ -17039,7 +17557,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W37" s="5"/>
+      <c r="W37" s="5">
+        <v>0</v>
+      </c>
       <c r="X37" s="1"/>
       <c r="Y37" s="5"/>
       <c r="Z37" s="5">
@@ -17082,7 +17602,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K38" s="5"/>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
       <c r="L38" s="1"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5">
@@ -17097,7 +17619,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q38" s="5"/>
+      <c r="Q38" s="5">
+        <v>0</v>
+      </c>
       <c r="R38" s="1"/>
       <c r="S38" s="5"/>
       <c r="T38" s="5">
@@ -17112,7 +17636,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W38" s="5"/>
+      <c r="W38" s="5">
+        <v>0</v>
+      </c>
       <c r="X38" s="1"/>
       <c r="Y38" s="5"/>
       <c r="Z38" s="5">
@@ -17155,7 +17681,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K39" s="5"/>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
       <c r="L39" s="1"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5">
@@ -17170,7 +17698,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q39" s="5"/>
+      <c r="Q39" s="5">
+        <v>0</v>
+      </c>
       <c r="R39" s="1"/>
       <c r="S39" s="5"/>
       <c r="T39" s="5">
@@ -17185,7 +17715,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W39" s="5"/>
+      <c r="W39" s="5">
+        <v>0</v>
+      </c>
       <c r="X39" s="1"/>
       <c r="Y39" s="5"/>
       <c r="Z39" s="5">
@@ -17228,7 +17760,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K40" s="5"/>
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
       <c r="L40" s="1"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5">
@@ -17243,7 +17777,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q40" s="5"/>
+      <c r="Q40" s="5">
+        <v>0</v>
+      </c>
       <c r="R40" s="1"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5">
@@ -17258,7 +17794,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W40" s="5"/>
+      <c r="W40" s="5">
+        <v>0</v>
+      </c>
       <c r="X40" s="1"/>
       <c r="Y40" s="5"/>
       <c r="Z40" s="5">
@@ -17301,7 +17839,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="K41" s="5"/>
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
       <c r="L41" s="1"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5">
@@ -17316,7 +17856,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="Q41" s="5"/>
+      <c r="Q41" s="5">
+        <v>0</v>
+      </c>
       <c r="R41" s="1"/>
       <c r="S41" s="5"/>
       <c r="T41" s="5">
@@ -17331,7 +17873,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3048</v>
       </c>
-      <c r="W41" s="5"/>
+      <c r="W41" s="5">
+        <v>0</v>
+      </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="5"/>
       <c r="Z41" s="5">
@@ -17375,7 +17919,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K43" s="5"/>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
       <c r="L43" s="1"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5">
@@ -17390,8 +17936,10 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="1"/>
+      <c r="Q43" s="5">
+        <v>0</v>
+      </c>
+      <c r="R43" s="5"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
         <f t="shared" si="4"/>
@@ -17405,7 +17953,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W43" s="5"/>
+      <c r="W43" s="5">
+        <v>0</v>
+      </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
@@ -17448,7 +17998,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K44" s="5"/>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
       <c r="L44" s="1"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5">
@@ -17463,7 +18015,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q44" s="5"/>
+      <c r="Q44" s="5">
+        <v>0</v>
+      </c>
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
@@ -17478,7 +18032,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W44" s="5"/>
+      <c r="W44" s="5">
+        <v>0</v>
+      </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
@@ -17521,7 +18077,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K45" s="5"/>
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
       <c r="L45" s="1"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5">
@@ -17536,7 +18094,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q45" s="5"/>
+      <c r="Q45" s="5">
+        <v>0</v>
+      </c>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
@@ -17551,7 +18111,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W45" s="5"/>
+      <c r="W45" s="5">
+        <v>0</v>
+      </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
@@ -17594,7 +18156,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K46" s="5"/>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
       <c r="L46" s="1"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
@@ -17609,7 +18173,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q46" s="5"/>
+      <c r="Q46" s="5">
+        <v>0</v>
+      </c>
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
@@ -17624,7 +18190,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W46" s="5"/>
+      <c r="W46" s="5">
+        <v>0</v>
+      </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
@@ -17667,7 +18235,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K47" s="5"/>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
       <c r="L47" s="1"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
@@ -17682,7 +18252,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q47" s="5"/>
+      <c r="Q47" s="5">
+        <v>0</v>
+      </c>
       <c r="R47" s="1"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5">
@@ -17697,7 +18269,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W47" s="5"/>
+      <c r="W47" s="5">
+        <v>0</v>
+      </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5">
@@ -17740,7 +18314,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K48" s="5"/>
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
       <c r="L48" s="1"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
@@ -17755,7 +18331,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q48" s="5"/>
+      <c r="Q48" s="5">
+        <v>0</v>
+      </c>
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
@@ -17770,7 +18348,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W48" s="5"/>
+      <c r="W48" s="5">
+        <v>0</v>
+      </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
@@ -17813,7 +18393,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K49" s="5"/>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
       <c r="L49" s="1"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5">
@@ -17828,7 +18410,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q49" s="5"/>
+      <c r="Q49" s="5">
+        <v>0</v>
+      </c>
       <c r="R49" s="1"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
@@ -17843,7 +18427,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W49" s="5"/>
+      <c r="W49" s="5">
+        <v>0</v>
+      </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5">
@@ -17886,7 +18472,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K50" s="5"/>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
       <c r="L50" s="1"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
@@ -17901,7 +18489,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q50" s="5"/>
+      <c r="Q50" s="5">
+        <v>0</v>
+      </c>
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
@@ -17916,7 +18506,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W50" s="5"/>
+      <c r="W50" s="5">
+        <v>0</v>
+      </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
@@ -17959,7 +18551,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K51" s="5"/>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
       <c r="L51" s="1"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
@@ -17974,7 +18568,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q51" s="5"/>
+      <c r="Q51" s="5">
+        <v>0</v>
+      </c>
       <c r="R51" s="1"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5">
@@ -17989,7 +18585,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W51" s="5"/>
+      <c r="W51" s="5">
+        <v>0</v>
+      </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5">
@@ -18032,7 +18630,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K52" s="5"/>
+      <c r="K52" s="5">
+        <v>0</v>
+      </c>
       <c r="L52" s="1"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5">
@@ -18047,7 +18647,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q52" s="5"/>
+      <c r="Q52" s="5">
+        <v>0</v>
+      </c>
       <c r="R52" s="1"/>
       <c r="S52" s="5"/>
       <c r="T52" s="5">
@@ -18062,7 +18664,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W52" s="5"/>
+      <c r="W52" s="5">
+        <v>0</v>
+      </c>
       <c r="X52" s="1"/>
       <c r="Y52" s="5"/>
       <c r="Z52" s="5">
@@ -18105,7 +18709,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="K53" s="5"/>
+      <c r="K53" s="5">
+        <v>0</v>
+      </c>
       <c r="L53" s="1"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
@@ -18120,7 +18726,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="Q53" s="5"/>
+      <c r="Q53" s="5">
+        <v>0</v>
+      </c>
       <c r="R53" s="1"/>
       <c r="S53" s="5"/>
       <c r="T53" s="5">
@@ -18135,7 +18743,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2800</v>
       </c>
-      <c r="W53" s="5"/>
+      <c r="W53" s="5">
+        <v>0</v>
+      </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="5"/>
       <c r="Z53" s="5">
@@ -18164,7 +18774,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="E55" s="5"/>
+      <c r="E55" s="5">
+        <v>0</v>
+      </c>
       <c r="F55" s="1"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5">
@@ -18221,7 +18833,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W55" s="5"/>
+      <c r="W55" s="5">
+        <v>0</v>
+      </c>
       <c r="X55" s="1"/>
       <c r="Y55" s="5"/>
       <c r="Z55" s="5">
@@ -18247,7 +18861,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="5">
+        <v>0</v>
+      </c>
       <c r="F56" s="1"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5">
@@ -18304,7 +18920,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W56" s="5"/>
+      <c r="W56" s="5">
+        <v>0</v>
+      </c>
       <c r="X56" s="1"/>
       <c r="Y56" s="5"/>
       <c r="Z56" s="5">
@@ -18330,7 +18948,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="5">
+        <v>0</v>
+      </c>
       <c r="F57" s="1"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5">
@@ -18387,7 +19007,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W57" s="5"/>
+      <c r="W57" s="5">
+        <v>0</v>
+      </c>
       <c r="X57" s="1"/>
       <c r="Y57" s="5"/>
       <c r="Z57" s="5">
@@ -18413,7 +19035,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="5">
+        <v>0</v>
+      </c>
       <c r="F58" s="1"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5">
@@ -18428,7 +19052,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K58" s="5"/>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
@@ -18464,7 +19090,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W58" s="5"/>
+      <c r="W58" s="5">
+        <v>0</v>
+      </c>
       <c r="X58" s="1"/>
       <c r="Y58" s="5"/>
       <c r="Z58" s="5">
@@ -18490,7 +19118,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="5">
+        <v>0</v>
+      </c>
       <c r="F59" s="1"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5">
@@ -18505,7 +19135,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K59" s="5"/>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
       <c r="L59" s="1"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5">
@@ -18541,7 +19173,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W59" s="5"/>
+      <c r="W59" s="5">
+        <v>0</v>
+      </c>
       <c r="X59" s="1"/>
       <c r="Y59" s="5"/>
       <c r="Z59" s="5">
@@ -18567,7 +19201,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="E60" s="5"/>
+      <c r="E60" s="5">
+        <v>0</v>
+      </c>
       <c r="F60" s="1"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5">
@@ -18582,7 +19218,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K60" s="5"/>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
       <c r="L60" s="1"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5">
@@ -18618,7 +19256,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W60" s="5"/>
+      <c r="W60" s="5">
+        <v>0</v>
+      </c>
       <c r="X60" s="1"/>
       <c r="Y60" s="5"/>
       <c r="Z60" s="5">
@@ -18644,7 +19284,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="5">
+        <v>0</v>
+      </c>
       <c r="F61" s="1"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5">
@@ -18659,7 +19301,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K61" s="5"/>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
       <c r="L61" s="1"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5">
@@ -18695,7 +19339,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W61" s="5"/>
+      <c r="W61" s="5">
+        <v>0</v>
+      </c>
       <c r="X61" s="1"/>
       <c r="Y61" s="5"/>
       <c r="Z61" s="5">
@@ -18721,7 +19367,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="E62" s="5"/>
+      <c r="E62" s="5">
+        <v>0</v>
+      </c>
       <c r="F62" s="1"/>
       <c r="G62" s="5"/>
       <c r="H62" s="5">
@@ -18736,7 +19384,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K62" s="5"/>
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
       <c r="L62" s="1"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5">
@@ -18772,7 +19422,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W62" s="5"/>
+      <c r="W62" s="5">
+        <v>0</v>
+      </c>
       <c r="X62" s="1"/>
       <c r="Y62" s="5"/>
       <c r="Z62" s="5">
@@ -18798,7 +19450,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="E63" s="5"/>
+      <c r="E63" s="5">
+        <v>0</v>
+      </c>
       <c r="F63" s="1"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5">
@@ -18813,7 +19467,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K63" s="5"/>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
       <c r="L63" s="1"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5">
@@ -18845,7 +19501,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W63" s="5"/>
+      <c r="W63" s="5">
+        <v>0</v>
+      </c>
       <c r="X63" s="1"/>
       <c r="Y63" s="5"/>
       <c r="Z63" s="5">
@@ -18871,7 +19529,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="E64" s="5"/>
+      <c r="E64" s="5">
+        <v>0</v>
+      </c>
       <c r="F64" s="1"/>
       <c r="G64" s="5"/>
       <c r="H64" s="5">
@@ -18886,7 +19546,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K64" s="5"/>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
       <c r="L64" s="1"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5">
@@ -18922,7 +19584,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W64" s="5"/>
+      <c r="W64" s="5">
+        <v>0</v>
+      </c>
       <c r="X64" s="1"/>
       <c r="Y64" s="5"/>
       <c r="Z64" s="5">
@@ -18948,7 +19612,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="E65" s="5"/>
+      <c r="E65" s="5">
+        <v>0</v>
+      </c>
       <c r="F65" s="1"/>
       <c r="G65" s="5"/>
       <c r="H65" s="5">
@@ -18963,7 +19629,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K65" s="5"/>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
       <c r="L65" s="1"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5">
@@ -18999,7 +19667,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="W65" s="5"/>
+      <c r="W65" s="5">
+        <v>0</v>
+      </c>
       <c r="X65" s="1"/>
       <c r="Y65" s="5"/>
       <c r="Z65" s="5">
@@ -19043,22 +19713,26 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K67" s="12"/>
+      <c r="K67" s="46">
+        <v>0</v>
+      </c>
       <c r="L67" s="10"/>
       <c r="M67" s="12"/>
       <c r="N67" s="12">
-        <f t="shared" si="2"/>
+        <f>IF((J67-K68)&lt;0,0,(J67-K68))</f>
         <v>5104</v>
       </c>
       <c r="O67" s="12">
-        <f t="shared" si="3"/>
+        <f>IF((K68-J67)&lt;0,0,(K68-J67))</f>
         <v>0</v>
       </c>
       <c r="P67" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="Q67" s="12"/>
+      <c r="Q67" s="12">
+        <v>0</v>
+      </c>
       <c r="R67" s="10"/>
       <c r="S67" s="12"/>
       <c r="T67" s="12">
@@ -19073,7 +19747,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W67" s="12"/>
+      <c r="W67" s="12">
+        <v>0</v>
+      </c>
       <c r="X67" s="10"/>
       <c r="Y67" s="12"/>
       <c r="Z67" s="12">
@@ -19116,22 +19792,26 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K68" s="12"/>
+      <c r="K68" s="46">
+        <v>0</v>
+      </c>
       <c r="L68" s="10"/>
       <c r="M68" s="12"/>
       <c r="N68" s="12">
-        <f t="shared" si="2"/>
+        <f>IF((J68-K69)&lt;0,0,(J68-K69))</f>
         <v>5104</v>
       </c>
       <c r="O68" s="12">
-        <f t="shared" si="3"/>
+        <f>IF((K69-J68)&lt;0,0,(K69-J68))</f>
         <v>0</v>
       </c>
       <c r="P68" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="Q68" s="12"/>
+      <c r="Q68" s="12">
+        <v>0</v>
+      </c>
       <c r="R68" s="10"/>
       <c r="S68" s="12"/>
       <c r="T68" s="12">
@@ -19146,7 +19826,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W68" s="12"/>
+      <c r="W68" s="12">
+        <v>0</v>
+      </c>
       <c r="X68" s="10"/>
       <c r="Y68" s="12"/>
       <c r="Z68" s="12">
@@ -19189,22 +19871,26 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K69" s="12"/>
+      <c r="K69" s="46">
+        <v>0</v>
+      </c>
       <c r="L69" s="10"/>
       <c r="M69" s="12"/>
       <c r="N69" s="12">
-        <f t="shared" si="2"/>
+        <f>IF((J69-K70)&lt;0,0,(J69-K70))</f>
         <v>5104</v>
       </c>
       <c r="O69" s="12">
-        <f t="shared" si="3"/>
+        <f>IF((K70-J69)&lt;0,0,(K70-J69))</f>
         <v>0</v>
       </c>
       <c r="P69" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="Q69" s="12"/>
+      <c r="Q69" s="12">
+        <v>0</v>
+      </c>
       <c r="R69" s="10"/>
       <c r="S69" s="12"/>
       <c r="T69" s="12">
@@ -19219,7 +19905,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W69" s="12"/>
+      <c r="W69" s="12">
+        <v>0</v>
+      </c>
       <c r="X69" s="10"/>
       <c r="Y69" s="12"/>
       <c r="Z69" s="12">
@@ -19262,22 +19950,26 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K70" s="12"/>
+      <c r="K70" s="46">
+        <v>0</v>
+      </c>
       <c r="L70" s="10"/>
       <c r="M70" s="12"/>
       <c r="N70" s="12">
-        <f t="shared" si="2"/>
+        <f>IF((J70-K71)&lt;0,0,(J70-K71))</f>
         <v>5104</v>
       </c>
       <c r="O70" s="12">
-        <f t="shared" si="3"/>
+        <f>IF((K71-J70)&lt;0,0,(K71-J70))</f>
         <v>0</v>
       </c>
       <c r="P70" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="Q70" s="12"/>
+      <c r="Q70" s="12">
+        <v>0</v>
+      </c>
       <c r="R70" s="10"/>
       <c r="S70" s="12"/>
       <c r="T70" s="12">
@@ -19292,7 +19984,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W70" s="12"/>
+      <c r="W70" s="12">
+        <v>0</v>
+      </c>
       <c r="X70" s="10"/>
       <c r="Y70" s="12"/>
       <c r="Z70" s="12">
@@ -19335,22 +20029,26 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K71" s="12"/>
+      <c r="K71" s="46">
+        <v>0</v>
+      </c>
       <c r="L71" s="10"/>
       <c r="M71" s="12"/>
       <c r="N71" s="12">
-        <f t="shared" ref="N71:N77" si="14">IF((J71-K71)&lt;0,0,(J71-K71))</f>
+        <f>IF((J71-K72)&lt;0,0,(J71-K72))</f>
         <v>5104</v>
       </c>
       <c r="O71" s="12">
-        <f t="shared" ref="O71:O77" si="15">IF((K71-J71)&lt;0,0,(K71-J71))</f>
+        <f>IF((K72-J71)&lt;0,0,(K72-J71))</f>
         <v>0</v>
       </c>
       <c r="P71" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="Q71" s="12"/>
+      <c r="Q71" s="12">
+        <v>0</v>
+      </c>
       <c r="R71" s="10"/>
       <c r="S71" s="12"/>
       <c r="T71" s="12">
@@ -19365,7 +20063,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W71" s="12"/>
+      <c r="W71" s="12">
+        <v>0</v>
+      </c>
       <c r="X71" s="10"/>
       <c r="Y71" s="12"/>
       <c r="Z71" s="12">
@@ -19408,22 +20108,26 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K72" s="12"/>
+      <c r="K72" s="46">
+        <v>0</v>
+      </c>
       <c r="L72" s="10"/>
       <c r="M72" s="12"/>
       <c r="N72" s="12">
-        <f t="shared" si="14"/>
+        <f>IF((J72-K73)&lt;0,0,(J72-K73))</f>
         <v>5104</v>
       </c>
       <c r="O72" s="12">
-        <f t="shared" si="15"/>
+        <f>IF((K73-J72)&lt;0,0,(K73-J72))</f>
         <v>0</v>
       </c>
       <c r="P72" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="Q72" s="12"/>
+      <c r="Q72" s="12">
+        <v>0</v>
+      </c>
       <c r="R72" s="10"/>
       <c r="S72" s="12"/>
       <c r="T72" s="12">
@@ -19438,7 +20142,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W72" s="12"/>
+      <c r="W72" s="12">
+        <v>0</v>
+      </c>
       <c r="X72" s="10"/>
       <c r="Y72" s="12"/>
       <c r="Z72" s="12">
@@ -19481,22 +20187,26 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K73" s="12"/>
+      <c r="K73" s="46">
+        <v>0</v>
+      </c>
       <c r="L73" s="10"/>
       <c r="M73" s="12"/>
       <c r="N73" s="12">
-        <f t="shared" si="14"/>
+        <f>IF((J73-K74)&lt;0,0,(J73-K74))</f>
         <v>5104</v>
       </c>
       <c r="O73" s="12">
-        <f t="shared" si="15"/>
+        <f>IF((K74-J73)&lt;0,0,(K74-J73))</f>
         <v>0</v>
       </c>
       <c r="P73" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="Q73" s="12"/>
+      <c r="Q73" s="12">
+        <v>0</v>
+      </c>
       <c r="R73" s="10"/>
       <c r="S73" s="12"/>
       <c r="T73" s="12">
@@ -19511,7 +20221,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W73" s="12"/>
+      <c r="W73" s="12">
+        <v>0</v>
+      </c>
       <c r="X73" s="10"/>
       <c r="Y73" s="12"/>
       <c r="Z73" s="12">
@@ -19554,45 +20266,51 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K74" s="12"/>
+      <c r="K74" s="46">
+        <v>0</v>
+      </c>
       <c r="L74" s="10"/>
       <c r="M74" s="12"/>
       <c r="N74" s="12">
-        <f t="shared" si="14"/>
+        <f>IF((J74-K75)&lt;0,0,(J74-K75))</f>
         <v>5104</v>
       </c>
       <c r="O74" s="12">
-        <f t="shared" si="15"/>
+        <f>IF((K75-J74)&lt;0,0,(K75-J74))</f>
         <v>0</v>
       </c>
       <c r="P74" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="Q74" s="12"/>
+      <c r="Q74" s="12">
+        <v>0</v>
+      </c>
       <c r="R74" s="10"/>
       <c r="S74" s="12"/>
       <c r="T74" s="12">
-        <f t="shared" ref="T74:T122" si="16">IF((P74-Q74)&lt;0,0,(P74-Q74))</f>
+        <f t="shared" ref="T74:T122" si="14">IF((P74-Q74)&lt;0,0,(P74-Q74))</f>
         <v>5104</v>
       </c>
       <c r="U74" s="12">
-        <f t="shared" ref="U74:U122" si="17">IF((Q74-P74)&lt;0,0,(Q74-P74))</f>
+        <f t="shared" ref="U74:U122" si="15">IF((Q74-P74)&lt;0,0,(Q74-P74))</f>
         <v>0</v>
       </c>
       <c r="V74" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W74" s="12"/>
+      <c r="W74" s="12">
+        <v>0</v>
+      </c>
       <c r="X74" s="10"/>
       <c r="Y74" s="12"/>
       <c r="Z74" s="12">
-        <f t="shared" ref="Z74:Z122" si="18">IF((V74-W74)&lt;0,0,(V74-W74))</f>
+        <f t="shared" ref="Z74:Z122" si="16">IF((V74-W74)&lt;0,0,(V74-W74))</f>
         <v>5104</v>
       </c>
       <c r="AA74" s="12">
-        <f t="shared" ref="AA74:AA122" si="19">IF((W74-V74)&lt;0,0,(W74-V74))</f>
+        <f t="shared" ref="AA74:AA122" si="17">IF((W74-V74)&lt;0,0,(W74-V74))</f>
         <v>0</v>
       </c>
     </row>
@@ -19627,45 +20345,51 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K75" s="12"/>
+      <c r="K75" s="46">
+        <v>0</v>
+      </c>
       <c r="L75" s="10"/>
       <c r="M75" s="12"/>
       <c r="N75" s="12">
-        <f t="shared" si="14"/>
+        <f>IF((J75-K76)&lt;0,0,(J75-K76))</f>
         <v>5104</v>
       </c>
       <c r="O75" s="12">
-        <f t="shared" si="15"/>
+        <f>IF((K76-J75)&lt;0,0,(K76-J75))</f>
         <v>0</v>
       </c>
       <c r="P75" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="Q75" s="12"/>
+      <c r="Q75" s="12">
+        <v>0</v>
+      </c>
       <c r="R75" s="10"/>
       <c r="S75" s="12"/>
       <c r="T75" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>5104</v>
       </c>
       <c r="U75" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V75" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W75" s="12"/>
+      <c r="W75" s="12">
+        <v>0</v>
+      </c>
       <c r="X75" s="10"/>
       <c r="Y75" s="12"/>
       <c r="Z75" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>5104</v>
       </c>
       <c r="AA75" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -19700,22 +20424,26 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K76" s="12"/>
+      <c r="K76" s="46">
+        <v>0</v>
+      </c>
       <c r="L76" s="10"/>
       <c r="M76" s="12"/>
       <c r="N76" s="12">
-        <f t="shared" si="14"/>
+        <f>IF((J76-K77)&lt;0,0,(J76-K77))</f>
         <v>5104</v>
       </c>
       <c r="O76" s="12">
-        <f t="shared" si="15"/>
+        <f>IF((K77-J76)&lt;0,0,(K77-J76))</f>
         <v>0</v>
       </c>
       <c r="P76" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="Q76" s="12"/>
+      <c r="Q76" s="12">
+        <v>0</v>
+      </c>
       <c r="R76" s="10"/>
       <c r="S76" s="12"/>
       <c r="T76" s="12">
@@ -19730,7 +20458,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W76" s="12"/>
+      <c r="W76" s="12">
+        <v>0</v>
+      </c>
       <c r="X76" s="10"/>
       <c r="Y76" s="12"/>
       <c r="Z76" s="12">
@@ -19773,45 +20503,51 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="K77" s="12"/>
+      <c r="K77" s="46">
+        <v>0</v>
+      </c>
       <c r="L77" s="10"/>
       <c r="M77" s="12"/>
       <c r="N77" s="12">
-        <f t="shared" si="14"/>
+        <f>IF((J77-K78)&lt;0,0,(J77-K78))</f>
         <v>5104</v>
       </c>
       <c r="O77" s="12">
-        <f t="shared" si="15"/>
+        <f>IF((K78-J77)&lt;0,0,(K78-J77))</f>
         <v>0</v>
       </c>
       <c r="P77" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="Q77" s="12"/>
+      <c r="Q77" s="12">
+        <v>0</v>
+      </c>
       <c r="R77" s="10"/>
       <c r="S77" s="12"/>
       <c r="T77" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>5104</v>
       </c>
       <c r="U77" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V77" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5104</v>
       </c>
-      <c r="W77" s="12"/>
+      <c r="W77" s="12">
+        <v>0</v>
+      </c>
       <c r="X77" s="10"/>
       <c r="Y77" s="12"/>
       <c r="Z77" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>5104</v>
       </c>
       <c r="AA77" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -19847,45 +20583,51 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K79" s="12"/>
+      <c r="K79" s="12">
+        <v>0</v>
+      </c>
       <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
-        <f t="shared" ref="N74:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
+        <f t="shared" ref="N79:N122" si="18">IF((J79-K79)&lt;0,0,(J79-K79))</f>
         <v>4992</v>
       </c>
       <c r="O79" s="12">
-        <f t="shared" ref="O74:O122" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
+        <f t="shared" ref="O79:O122" si="19">IF((K79-J79)&lt;0,0,(K79-J79))</f>
         <v>0</v>
       </c>
       <c r="P79" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="Q79" s="12"/>
+      <c r="Q79" s="12">
+        <v>0</v>
+      </c>
       <c r="R79" s="10"/>
       <c r="S79" s="12"/>
       <c r="T79" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4992</v>
       </c>
       <c r="U79" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V79" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W79" s="12"/>
+      <c r="W79" s="12">
+        <v>0</v>
+      </c>
       <c r="X79" s="10"/>
       <c r="Y79" s="12"/>
       <c r="Z79" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4992</v>
       </c>
       <c r="AA79" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -19920,45 +20662,51 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K80" s="12"/>
+      <c r="K80" s="12">
+        <v>0</v>
+      </c>
       <c r="L80" s="10"/>
       <c r="M80" s="12"/>
       <c r="N80" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>4992</v>
       </c>
       <c r="O80" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P80" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="Q80" s="12"/>
+      <c r="Q80" s="12">
+        <v>0</v>
+      </c>
       <c r="R80" s="10"/>
       <c r="S80" s="12"/>
       <c r="T80" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4992</v>
       </c>
       <c r="U80" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V80" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W80" s="12"/>
+      <c r="W80" s="12">
+        <v>0</v>
+      </c>
       <c r="X80" s="10"/>
       <c r="Y80" s="12"/>
       <c r="Z80" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4992</v>
       </c>
       <c r="AA80" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -19993,45 +20741,51 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K81" s="12"/>
+      <c r="K81" s="12">
+        <v>0</v>
+      </c>
       <c r="L81" s="10"/>
       <c r="M81" s="12"/>
       <c r="N81" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>4992</v>
       </c>
       <c r="O81" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P81" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="Q81" s="12"/>
+      <c r="Q81" s="12">
+        <v>0</v>
+      </c>
       <c r="R81" s="10"/>
       <c r="S81" s="12"/>
       <c r="T81" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4992</v>
       </c>
       <c r="U81" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V81" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W81" s="12"/>
+      <c r="W81" s="12">
+        <v>0</v>
+      </c>
       <c r="X81" s="10"/>
       <c r="Y81" s="12"/>
       <c r="Z81" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4992</v>
       </c>
       <c r="AA81" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -20066,45 +20820,51 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K82" s="12"/>
+      <c r="K82" s="12">
+        <v>0</v>
+      </c>
       <c r="L82" s="10"/>
       <c r="M82" s="12"/>
       <c r="N82" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>4992</v>
       </c>
       <c r="O82" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P82" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="Q82" s="12"/>
+      <c r="Q82" s="12">
+        <v>0</v>
+      </c>
       <c r="R82" s="10"/>
       <c r="S82" s="12"/>
       <c r="T82" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4992</v>
       </c>
       <c r="U82" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V82" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W82" s="12"/>
+      <c r="W82" s="12">
+        <v>0</v>
+      </c>
       <c r="X82" s="10"/>
       <c r="Y82" s="12"/>
       <c r="Z82" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4992</v>
       </c>
       <c r="AA82" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -20139,45 +20899,51 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K83" s="12"/>
+      <c r="K83" s="12">
+        <v>0</v>
+      </c>
       <c r="L83" s="10"/>
       <c r="M83" s="12"/>
       <c r="N83" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>4992</v>
       </c>
       <c r="O83" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P83" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="Q83" s="12"/>
+      <c r="Q83" s="12">
+        <v>0</v>
+      </c>
       <c r="R83" s="10"/>
       <c r="S83" s="12"/>
       <c r="T83" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4992</v>
       </c>
       <c r="U83" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V83" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W83" s="12"/>
+      <c r="W83" s="12">
+        <v>0</v>
+      </c>
       <c r="X83" s="10"/>
       <c r="Y83" s="12"/>
       <c r="Z83" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4992</v>
       </c>
       <c r="AA83" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -20201,56 +20967,62 @@
       <c r="F84" s="10"/>
       <c r="G84" s="12"/>
       <c r="H84" s="12">
-        <f t="shared" ref="H84:H122" si="22">IF((D84-E84)&lt;0,0,(D84-E84))</f>
+        <f t="shared" ref="H84:H122" si="20">IF((D84-E84)&lt;0,0,(D84-E84))</f>
         <v>4992</v>
       </c>
       <c r="I84" s="12">
-        <f t="shared" ref="I84:I122" si="23">IF((E84-D84)&lt;0,0,(E84-D84))</f>
+        <f t="shared" ref="I84:I122" si="21">IF((E84-D84)&lt;0,0,(E84-D84))</f>
         <v>0</v>
       </c>
       <c r="J84" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K84" s="12"/>
+      <c r="K84" s="12">
+        <v>0</v>
+      </c>
       <c r="L84" s="10"/>
       <c r="M84" s="12"/>
       <c r="N84" s="12">
-        <f t="shared" ref="N84:N89" si="24">IF((J84-K84)&lt;0,0,(J84-K84))</f>
+        <f t="shared" ref="N84:N89" si="22">IF((J84-K84)&lt;0,0,(J84-K84))</f>
         <v>4992</v>
       </c>
       <c r="O84" s="12">
-        <f t="shared" ref="O84:O89" si="25">IF((K84-J84)&lt;0,0,(K84-J84))</f>
+        <f t="shared" ref="O84:O89" si="23">IF((K84-J84)&lt;0,0,(K84-J84))</f>
         <v>0</v>
       </c>
       <c r="P84" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="Q84" s="12"/>
+      <c r="Q84" s="12">
+        <v>0</v>
+      </c>
       <c r="R84" s="10"/>
       <c r="S84" s="12"/>
       <c r="T84" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4992</v>
       </c>
       <c r="U84" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V84" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W84" s="12"/>
+      <c r="W84" s="12">
+        <v>0</v>
+      </c>
       <c r="X84" s="10"/>
       <c r="Y84" s="12"/>
       <c r="Z84" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4992</v>
       </c>
       <c r="AA84" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -20285,22 +21057,26 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K85" s="12"/>
+      <c r="K85" s="12">
+        <v>0</v>
+      </c>
       <c r="L85" s="10"/>
       <c r="M85" s="12"/>
       <c r="N85" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>4992</v>
       </c>
       <c r="O85" s="12">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="P85" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="Q85" s="12"/>
+      <c r="Q85" s="12">
+        <v>0</v>
+      </c>
       <c r="R85" s="10"/>
       <c r="S85" s="12"/>
       <c r="T85" s="12">
@@ -20315,7 +21091,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W85" s="12"/>
+      <c r="W85" s="12">
+        <v>0</v>
+      </c>
       <c r="X85" s="10"/>
       <c r="Y85" s="12"/>
       <c r="Z85" s="12">
@@ -20347,56 +21125,62 @@
       <c r="F86" s="10"/>
       <c r="G86" s="12"/>
       <c r="H86" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4992</v>
       </c>
       <c r="I86" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J86" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K86" s="12"/>
+      <c r="K86" s="12">
+        <v>0</v>
+      </c>
       <c r="L86" s="10"/>
       <c r="M86" s="12"/>
       <c r="N86" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>4992</v>
       </c>
       <c r="O86" s="12">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="P86" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="Q86" s="12"/>
+      <c r="Q86" s="12">
+        <v>0</v>
+      </c>
       <c r="R86" s="10"/>
       <c r="S86" s="12"/>
       <c r="T86" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4992</v>
       </c>
       <c r="U86" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V86" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W86" s="12"/>
+      <c r="W86" s="12">
+        <v>0</v>
+      </c>
       <c r="X86" s="10"/>
       <c r="Y86" s="12"/>
       <c r="Z86" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4992</v>
       </c>
       <c r="AA86" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -20420,56 +21204,62 @@
       <c r="F87" s="10"/>
       <c r="G87" s="12"/>
       <c r="H87" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4992</v>
       </c>
       <c r="I87" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J87" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K87" s="12"/>
+      <c r="K87" s="12">
+        <v>0</v>
+      </c>
       <c r="L87" s="10"/>
       <c r="M87" s="12"/>
       <c r="N87" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>4992</v>
       </c>
       <c r="O87" s="12">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="P87" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="Q87" s="12"/>
+      <c r="Q87" s="12">
+        <v>0</v>
+      </c>
       <c r="R87" s="10"/>
       <c r="S87" s="12"/>
       <c r="T87" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4992</v>
       </c>
       <c r="U87" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V87" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W87" s="12"/>
+      <c r="W87" s="12">
+        <v>0</v>
+      </c>
       <c r="X87" s="10"/>
       <c r="Y87" s="12"/>
       <c r="Z87" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4992</v>
       </c>
       <c r="AA87" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -20504,22 +21294,26 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K88" s="12"/>
+      <c r="K88" s="12">
+        <v>0</v>
+      </c>
       <c r="L88" s="10"/>
       <c r="M88" s="12"/>
       <c r="N88" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>4992</v>
       </c>
       <c r="O88" s="12">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="P88" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="Q88" s="12"/>
+      <c r="Q88" s="12">
+        <v>0</v>
+      </c>
       <c r="R88" s="10"/>
       <c r="S88" s="12"/>
       <c r="T88" s="12">
@@ -20534,7 +21328,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W88" s="12"/>
+      <c r="W88" s="12">
+        <v>0</v>
+      </c>
       <c r="X88" s="10"/>
       <c r="Y88" s="12"/>
       <c r="Z88" s="12">
@@ -20566,56 +21362,62 @@
       <c r="F89" s="10"/>
       <c r="G89" s="12"/>
       <c r="H89" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4992</v>
       </c>
       <c r="I89" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J89" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="K89" s="12"/>
+      <c r="K89" s="12">
+        <v>0</v>
+      </c>
       <c r="L89" s="10"/>
       <c r="M89" s="12"/>
       <c r="N89" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>4992</v>
       </c>
       <c r="O89" s="12">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="P89" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="Q89" s="12"/>
+      <c r="Q89" s="12">
+        <v>0</v>
+      </c>
       <c r="R89" s="10"/>
       <c r="S89" s="12"/>
       <c r="T89" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4992</v>
       </c>
       <c r="U89" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V89" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4992</v>
       </c>
-      <c r="W89" s="12"/>
+      <c r="W89" s="12">
+        <v>0</v>
+      </c>
       <c r="X89" s="10"/>
       <c r="Y89" s="12"/>
       <c r="Z89" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4992</v>
       </c>
       <c r="AA89" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -20640,26 +21442,28 @@
       <c r="F91" s="10"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4792</v>
       </c>
       <c r="I91" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J91" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K91" s="12"/>
+      <c r="K91" s="12">
+        <v>0</v>
+      </c>
       <c r="L91" s="10"/>
       <c r="M91" s="12"/>
       <c r="N91" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>4792</v>
       </c>
       <c r="O91" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P91" s="12">
@@ -20676,32 +21480,32 @@
         <v>62</v>
       </c>
       <c r="T91" s="12">
+        <f t="shared" si="14"/>
+        <v>4700</v>
+      </c>
+      <c r="U91" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V91" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4792</v>
+      </c>
+      <c r="W91" s="12">
+        <v>92</v>
+      </c>
+      <c r="X91" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y91" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z91" s="12">
         <f t="shared" si="16"/>
         <v>4700</v>
       </c>
-      <c r="U91" s="12">
+      <c r="AA91" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V91" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4792</v>
-      </c>
-      <c r="W91" s="12">
-        <v>92</v>
-      </c>
-      <c r="X91" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y91" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z91" s="12">
-        <f t="shared" si="18"/>
-        <v>4700</v>
-      </c>
-      <c r="AA91" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -20725,11 +21529,11 @@
       <c r="F92" s="10"/>
       <c r="G92" s="12"/>
       <c r="H92" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4792</v>
       </c>
       <c r="I92" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J92" s="12">
@@ -20746,11 +21550,11 @@
         <v>62</v>
       </c>
       <c r="N92" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>4693</v>
       </c>
       <c r="O92" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P92" s="12">
@@ -20763,11 +21567,11 @@
       <c r="R92" s="10"/>
       <c r="S92" s="12"/>
       <c r="T92" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4792</v>
       </c>
       <c r="U92" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V92" s="12">
@@ -20784,11 +21588,11 @@
         <v>62</v>
       </c>
       <c r="Z92" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4700</v>
       </c>
       <c r="AA92" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -20812,11 +21616,11 @@
       <c r="F93" s="10"/>
       <c r="G93" s="12"/>
       <c r="H93" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4792</v>
       </c>
       <c r="I93" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J93" s="12">
@@ -20833,11 +21637,11 @@
         <v>62</v>
       </c>
       <c r="N93" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>4693</v>
       </c>
       <c r="O93" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P93" s="12">
@@ -20850,11 +21654,11 @@
       <c r="R93" s="10"/>
       <c r="S93" s="12"/>
       <c r="T93" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4792</v>
       </c>
       <c r="U93" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V93" s="12">
@@ -20871,11 +21675,11 @@
         <v>62</v>
       </c>
       <c r="Z93" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4700</v>
       </c>
       <c r="AA93" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -20899,26 +21703,28 @@
       <c r="F94" s="10"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4792</v>
       </c>
       <c r="I94" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J94" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K94" s="12"/>
+      <c r="K94" s="12">
+        <v>0</v>
+      </c>
       <c r="L94" s="10"/>
       <c r="M94" s="12"/>
       <c r="N94" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>4792</v>
       </c>
       <c r="O94" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P94" s="12">
@@ -20935,32 +21741,32 @@
         <v>62</v>
       </c>
       <c r="T94" s="12">
+        <f t="shared" si="14"/>
+        <v>4700</v>
+      </c>
+      <c r="U94" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V94" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4792</v>
+      </c>
+      <c r="W94" s="12">
+        <v>92</v>
+      </c>
+      <c r="X94" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y94" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z94" s="12">
         <f t="shared" si="16"/>
         <v>4700</v>
       </c>
-      <c r="U94" s="12">
+      <c r="AA94" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V94" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4792</v>
-      </c>
-      <c r="W94" s="12">
-        <v>92</v>
-      </c>
-      <c r="X94" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y94" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z94" s="12">
-        <f t="shared" si="18"/>
-        <v>4700</v>
-      </c>
-      <c r="AA94" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -20984,26 +21790,28 @@
       <c r="F95" s="10"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4792</v>
       </c>
       <c r="I95" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J95" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K95" s="12"/>
+      <c r="K95" s="12">
+        <v>0</v>
+      </c>
       <c r="L95" s="10"/>
       <c r="M95" s="12"/>
       <c r="N95" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>4792</v>
       </c>
       <c r="O95" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P95" s="12">
@@ -21020,32 +21828,32 @@
         <v>62</v>
       </c>
       <c r="T95" s="12">
+        <f t="shared" si="14"/>
+        <v>4700</v>
+      </c>
+      <c r="U95" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V95" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4792</v>
+      </c>
+      <c r="W95" s="12">
+        <v>92</v>
+      </c>
+      <c r="X95" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y95" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z95" s="12">
         <f t="shared" si="16"/>
         <v>4700</v>
       </c>
-      <c r="U95" s="12">
+      <c r="AA95" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V95" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4792</v>
-      </c>
-      <c r="W95" s="12">
-        <v>92</v>
-      </c>
-      <c r="X95" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y95" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z95" s="12">
-        <f t="shared" si="18"/>
-        <v>4700</v>
-      </c>
-      <c r="AA95" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -21069,26 +21877,28 @@
       <c r="F96" s="10"/>
       <c r="G96" s="12"/>
       <c r="H96" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4792</v>
       </c>
       <c r="I96" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J96" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K96" s="12"/>
+      <c r="K96" s="12">
+        <v>0</v>
+      </c>
       <c r="L96" s="10"/>
       <c r="M96" s="12"/>
       <c r="N96" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>4792</v>
       </c>
       <c r="O96" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P96" s="12">
@@ -21105,32 +21915,32 @@
         <v>62</v>
       </c>
       <c r="T96" s="12">
+        <f t="shared" si="14"/>
+        <v>4700</v>
+      </c>
+      <c r="U96" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V96" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4792</v>
+      </c>
+      <c r="W96" s="12">
+        <v>92</v>
+      </c>
+      <c r="X96" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y96" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z96" s="12">
         <f t="shared" si="16"/>
         <v>4700</v>
       </c>
-      <c r="U96" s="12">
+      <c r="AA96" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V96" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4792</v>
-      </c>
-      <c r="W96" s="12">
-        <v>92</v>
-      </c>
-      <c r="X96" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y96" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z96" s="12">
-        <f t="shared" si="18"/>
-        <v>4700</v>
-      </c>
-      <c r="AA96" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -21165,15 +21975,17 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K97" s="12"/>
+      <c r="K97" s="12">
+        <v>0</v>
+      </c>
       <c r="L97" s="10"/>
       <c r="M97" s="12"/>
       <c r="N97" s="12">
-        <f t="shared" ref="N97:N101" si="26">IF((J97-K97)&lt;0,0,(J97-K97))</f>
+        <f t="shared" ref="N97:N101" si="24">IF((J97-K97)&lt;0,0,(J97-K97))</f>
         <v>4792</v>
       </c>
       <c r="O97" s="12">
-        <f t="shared" ref="O97:O101" si="27">IF((K97-J97)&lt;0,0,(K97-J97))</f>
+        <f t="shared" ref="O97:O101" si="25">IF((K97-J97)&lt;0,0,(K97-J97))</f>
         <v>0</v>
       </c>
       <c r="P97" s="12">
@@ -21235,26 +22047,28 @@
       <c r="F98" s="10"/>
       <c r="G98" s="12"/>
       <c r="H98" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4792</v>
       </c>
       <c r="I98" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J98" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K98" s="12"/>
+      <c r="K98" s="12">
+        <v>0</v>
+      </c>
       <c r="L98" s="10"/>
       <c r="M98" s="12"/>
       <c r="N98" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>4792</v>
       </c>
       <c r="O98" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="P98" s="12">
@@ -21267,11 +22081,11 @@
       <c r="R98" s="10"/>
       <c r="S98" s="12"/>
       <c r="T98" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4792</v>
       </c>
       <c r="U98" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V98" s="12">
@@ -21288,11 +22102,11 @@
         <v>62</v>
       </c>
       <c r="Z98" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4700</v>
       </c>
       <c r="AA98" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -21316,26 +22130,28 @@
       <c r="F99" s="10"/>
       <c r="G99" s="12"/>
       <c r="H99" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4792</v>
       </c>
       <c r="I99" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J99" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K99" s="12"/>
+      <c r="K99" s="12">
+        <v>0</v>
+      </c>
       <c r="L99" s="10"/>
       <c r="M99" s="12"/>
       <c r="N99" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>4792</v>
       </c>
       <c r="O99" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="P99" s="12">
@@ -21348,11 +22164,11 @@
       <c r="R99" s="10"/>
       <c r="S99" s="12"/>
       <c r="T99" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>4792</v>
       </c>
       <c r="U99" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V99" s="12">
@@ -21365,11 +22181,11 @@
       <c r="X99" s="10"/>
       <c r="Y99" s="12"/>
       <c r="Z99" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4792</v>
       </c>
       <c r="AA99" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -21404,15 +22220,17 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K100" s="12"/>
+      <c r="K100" s="12">
+        <v>0</v>
+      </c>
       <c r="L100" s="10"/>
       <c r="M100" s="12"/>
       <c r="N100" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>4792</v>
       </c>
       <c r="O100" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="P100" s="12">
@@ -21478,26 +22296,28 @@
       <c r="F101" s="10"/>
       <c r="G101" s="12"/>
       <c r="H101" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4792</v>
       </c>
       <c r="I101" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J101" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4792</v>
       </c>
-      <c r="K101" s="12"/>
+      <c r="K101" s="12">
+        <v>0</v>
+      </c>
       <c r="L101" s="10"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>4792</v>
       </c>
       <c r="O101" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="P101" s="12">
@@ -21514,32 +22334,32 @@
         <v>62</v>
       </c>
       <c r="T101" s="12">
+        <f t="shared" si="14"/>
+        <v>4700</v>
+      </c>
+      <c r="U101" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V101" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>4792</v>
+      </c>
+      <c r="W101" s="12">
+        <v>92</v>
+      </c>
+      <c r="X101" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y101" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z101" s="12">
         <f t="shared" si="16"/>
         <v>4700</v>
       </c>
-      <c r="U101" s="12">
+      <c r="AA101" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V101" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>4792</v>
-      </c>
-      <c r="W101" s="12">
-        <v>92</v>
-      </c>
-      <c r="X101" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y101" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z101" s="12">
-        <f t="shared" si="18"/>
-        <v>4700</v>
-      </c>
-      <c r="AA101" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -21564,11 +22384,11 @@
       <c r="F103" s="10"/>
       <c r="G103" s="12"/>
       <c r="H103" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>3200</v>
       </c>
       <c r="I103" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J103" s="12">
@@ -21585,11 +22405,11 @@
         <v>62</v>
       </c>
       <c r="N103" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>3118</v>
       </c>
       <c r="O103" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P103" s="12">
@@ -21606,32 +22426,32 @@
         <v>62</v>
       </c>
       <c r="T103" s="12">
+        <f t="shared" si="14"/>
+        <v>3108</v>
+      </c>
+      <c r="U103" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V103" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3200</v>
+      </c>
+      <c r="W103" s="12">
+        <v>92</v>
+      </c>
+      <c r="X103" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y103" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z103" s="12">
         <f t="shared" si="16"/>
         <v>3108</v>
       </c>
-      <c r="U103" s="12">
+      <c r="AA103" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V103" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3200</v>
-      </c>
-      <c r="W103" s="12">
-        <v>92</v>
-      </c>
-      <c r="X103" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y103" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z103" s="12">
-        <f t="shared" si="18"/>
-        <v>3108</v>
-      </c>
-      <c r="AA103" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -21655,11 +22475,11 @@
       <c r="F104" s="10"/>
       <c r="G104" s="12"/>
       <c r="H104" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>3200</v>
       </c>
       <c r="I104" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J104" s="12">
@@ -21672,11 +22492,11 @@
       <c r="L104" s="10"/>
       <c r="M104" s="12"/>
       <c r="N104" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>3200</v>
       </c>
       <c r="O104" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P104" s="12">
@@ -21693,32 +22513,32 @@
         <v>62</v>
       </c>
       <c r="T104" s="12">
+        <f t="shared" si="14"/>
+        <v>3108</v>
+      </c>
+      <c r="U104" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V104" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3200</v>
+      </c>
+      <c r="W104" s="12">
+        <v>92</v>
+      </c>
+      <c r="X104" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y104" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z104" s="12">
         <f t="shared" si="16"/>
         <v>3108</v>
       </c>
-      <c r="U104" s="12">
+      <c r="AA104" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V104" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3200</v>
-      </c>
-      <c r="W104" s="12">
-        <v>92</v>
-      </c>
-      <c r="X104" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y104" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z104" s="12">
-        <f t="shared" si="18"/>
-        <v>3108</v>
-      </c>
-      <c r="AA104" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -21746,11 +22566,11 @@
         <v>62</v>
       </c>
       <c r="H105" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>3044</v>
       </c>
       <c r="I105" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J105" s="12">
@@ -21767,11 +22587,11 @@
         <v>62</v>
       </c>
       <c r="N105" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>3118</v>
       </c>
       <c r="O105" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P105" s="12">
@@ -21788,32 +22608,32 @@
         <v>62</v>
       </c>
       <c r="T105" s="12">
+        <f t="shared" si="14"/>
+        <v>3108</v>
+      </c>
+      <c r="U105" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V105" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3200</v>
+      </c>
+      <c r="W105" s="12">
+        <v>92</v>
+      </c>
+      <c r="X105" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y105" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z105" s="12">
         <f t="shared" si="16"/>
         <v>3108</v>
       </c>
-      <c r="U105" s="12">
+      <c r="AA105" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V105" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3200</v>
-      </c>
-      <c r="W105" s="12">
-        <v>92</v>
-      </c>
-      <c r="X105" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y105" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z105" s="12">
-        <f t="shared" si="18"/>
-        <v>3108</v>
-      </c>
-      <c r="AA105" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -21837,11 +22657,11 @@
       <c r="F106" s="10"/>
       <c r="G106" s="12"/>
       <c r="H106" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>3200</v>
       </c>
       <c r="I106" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J106" s="12">
@@ -21854,11 +22674,11 @@
       <c r="L106" s="10"/>
       <c r="M106" s="12"/>
       <c r="N106" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>3200</v>
       </c>
       <c r="O106" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P106" s="12">
@@ -21875,32 +22695,32 @@
         <v>62</v>
       </c>
       <c r="T106" s="12">
+        <f t="shared" si="14"/>
+        <v>3108</v>
+      </c>
+      <c r="U106" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V106" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3200</v>
+      </c>
+      <c r="W106" s="12">
+        <v>92</v>
+      </c>
+      <c r="X106" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y106" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z106" s="12">
         <f t="shared" si="16"/>
         <v>3108</v>
       </c>
-      <c r="U106" s="12">
+      <c r="AA106" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V106" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3200</v>
-      </c>
-      <c r="W106" s="12">
-        <v>92</v>
-      </c>
-      <c r="X106" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y106" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z106" s="12">
-        <f t="shared" si="18"/>
-        <v>3108</v>
-      </c>
-      <c r="AA106" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -21924,11 +22744,11 @@
       <c r="F107" s="10"/>
       <c r="G107" s="12"/>
       <c r="H107" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>3200</v>
       </c>
       <c r="I107" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J107" s="12">
@@ -21941,11 +22761,11 @@
       <c r="L107" s="10"/>
       <c r="M107" s="12"/>
       <c r="N107" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>3200</v>
       </c>
       <c r="O107" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P107" s="12">
@@ -21962,32 +22782,32 @@
         <v>62</v>
       </c>
       <c r="T107" s="12">
+        <f t="shared" si="14"/>
+        <v>3108</v>
+      </c>
+      <c r="U107" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V107" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3200</v>
+      </c>
+      <c r="W107" s="12">
+        <v>92</v>
+      </c>
+      <c r="X107" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y107" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z107" s="12">
         <f t="shared" si="16"/>
         <v>3108</v>
       </c>
-      <c r="U107" s="12">
+      <c r="AA107" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V107" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3200</v>
-      </c>
-      <c r="W107" s="12">
-        <v>92</v>
-      </c>
-      <c r="X107" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y107" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z107" s="12">
-        <f t="shared" si="18"/>
-        <v>3108</v>
-      </c>
-      <c r="AA107" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -22011,11 +22831,11 @@
       <c r="F108" s="10"/>
       <c r="G108" s="12"/>
       <c r="H108" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>3200</v>
       </c>
       <c r="I108" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J108" s="12">
@@ -22028,11 +22848,11 @@
       <c r="L108" s="10"/>
       <c r="M108" s="12"/>
       <c r="N108" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>3200</v>
       </c>
       <c r="O108" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P108" s="12">
@@ -22049,32 +22869,32 @@
         <v>62</v>
       </c>
       <c r="T108" s="12">
+        <f t="shared" si="14"/>
+        <v>3108</v>
+      </c>
+      <c r="U108" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V108" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3200</v>
+      </c>
+      <c r="W108" s="12">
+        <v>92</v>
+      </c>
+      <c r="X108" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y108" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z108" s="12">
         <f t="shared" si="16"/>
         <v>3108</v>
       </c>
-      <c r="U108" s="12">
+      <c r="AA108" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V108" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3200</v>
-      </c>
-      <c r="W108" s="12">
-        <v>92</v>
-      </c>
-      <c r="X108" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y108" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z108" s="12">
-        <f t="shared" si="18"/>
-        <v>3108</v>
-      </c>
-      <c r="AA108" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -22115,11 +22935,11 @@
       <c r="L109" s="10"/>
       <c r="M109" s="12"/>
       <c r="N109" s="12">
-        <f t="shared" ref="N109:N113" si="28">IF((J109-K109)&lt;0,0,(J109-K109))</f>
+        <f t="shared" ref="N109:N113" si="26">IF((J109-K109)&lt;0,0,(J109-K109))</f>
         <v>3200</v>
       </c>
       <c r="O109" s="12">
-        <f t="shared" ref="O109:O113" si="29">IF((K109-J109)&lt;0,0,(K109-J109))</f>
+        <f t="shared" ref="O109:O113" si="27">IF((K109-J109)&lt;0,0,(K109-J109))</f>
         <v>0</v>
       </c>
       <c r="P109" s="12">
@@ -22185,11 +23005,11 @@
       <c r="F110" s="10"/>
       <c r="G110" s="12"/>
       <c r="H110" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>3200</v>
       </c>
       <c r="I110" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J110" s="12">
@@ -22202,11 +23022,11 @@
       <c r="L110" s="10"/>
       <c r="M110" s="12"/>
       <c r="N110" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>3200</v>
       </c>
       <c r="O110" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P110" s="12">
@@ -22223,32 +23043,32 @@
         <v>62</v>
       </c>
       <c r="T110" s="12">
+        <f t="shared" si="14"/>
+        <v>3108</v>
+      </c>
+      <c r="U110" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V110" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3200</v>
+      </c>
+      <c r="W110" s="12">
+        <v>92</v>
+      </c>
+      <c r="X110" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y110" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z110" s="12">
         <f t="shared" si="16"/>
         <v>3108</v>
       </c>
-      <c r="U110" s="12">
+      <c r="AA110" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V110" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3200</v>
-      </c>
-      <c r="W110" s="12">
-        <v>92</v>
-      </c>
-      <c r="X110" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y110" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z110" s="12">
-        <f t="shared" si="18"/>
-        <v>3108</v>
-      </c>
-      <c r="AA110" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -22272,11 +23092,11 @@
       <c r="F111" s="10"/>
       <c r="G111" s="12"/>
       <c r="H111" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>3200</v>
       </c>
       <c r="I111" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J111" s="12">
@@ -22289,11 +23109,11 @@
       <c r="L111" s="10"/>
       <c r="M111" s="12"/>
       <c r="N111" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>3200</v>
       </c>
       <c r="O111" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P111" s="12">
@@ -22306,11 +23126,11 @@
       <c r="R111" s="10"/>
       <c r="S111" s="12"/>
       <c r="T111" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>3200</v>
       </c>
       <c r="U111" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V111" s="12">
@@ -22323,11 +23143,11 @@
       <c r="X111" s="10"/>
       <c r="Y111" s="12"/>
       <c r="Z111" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>3200</v>
       </c>
       <c r="AA111" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -22368,11 +23188,11 @@
       <c r="L112" s="10"/>
       <c r="M112" s="12"/>
       <c r="N112" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>3200</v>
       </c>
       <c r="O112" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P112" s="12">
@@ -22434,11 +23254,11 @@
       <c r="F113" s="10"/>
       <c r="G113" s="12"/>
       <c r="H113" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>3200</v>
       </c>
       <c r="I113" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J113" s="12">
@@ -22451,11 +23271,11 @@
       <c r="L113" s="10"/>
       <c r="M113" s="12"/>
       <c r="N113" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>3200</v>
       </c>
       <c r="O113" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P113" s="12">
@@ -22472,32 +23292,32 @@
         <v>62</v>
       </c>
       <c r="T113" s="12">
+        <f t="shared" si="14"/>
+        <v>3108</v>
+      </c>
+      <c r="U113" s="12">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V113" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>3200</v>
+      </c>
+      <c r="W113" s="12">
+        <v>92</v>
+      </c>
+      <c r="X113" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y113" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z113" s="12">
         <f t="shared" si="16"/>
         <v>3108</v>
       </c>
-      <c r="U113" s="12">
+      <c r="AA113" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V113" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>3200</v>
-      </c>
-      <c r="W113" s="12">
-        <v>92</v>
-      </c>
-      <c r="X113" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y113" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z113" s="12">
-        <f t="shared" si="18"/>
-        <v>3108</v>
-      </c>
-      <c r="AA113" s="12">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -22522,26 +23342,28 @@
       <c r="F115" s="1"/>
       <c r="G115" s="5"/>
       <c r="H115" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1408</v>
       </c>
       <c r="I115" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J115" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K115" s="5"/>
+      <c r="K115" s="5">
+        <v>0</v>
+      </c>
       <c r="L115" s="1"/>
       <c r="M115" s="5"/>
       <c r="N115" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1408</v>
       </c>
       <c r="O115" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P115" s="5">
@@ -22552,26 +23374,28 @@
       <c r="R115" s="1"/>
       <c r="S115" s="5"/>
       <c r="T115" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1408</v>
       </c>
       <c r="U115" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V115" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W115" s="5"/>
+      <c r="W115" s="5">
+        <v>0</v>
+      </c>
       <c r="X115" s="1"/>
       <c r="Y115" s="5"/>
       <c r="Z115" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1408</v>
       </c>
       <c r="AA115" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -22595,26 +23419,28 @@
       <c r="F116" s="1"/>
       <c r="G116" s="5"/>
       <c r="H116" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1408</v>
       </c>
       <c r="I116" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J116" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K116" s="5"/>
+      <c r="K116" s="5">
+        <v>0</v>
+      </c>
       <c r="L116" s="1"/>
       <c r="M116" s="5"/>
       <c r="N116" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1408</v>
       </c>
       <c r="O116" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P116" s="5">
@@ -22625,26 +23451,28 @@
       <c r="R116" s="1"/>
       <c r="S116" s="5"/>
       <c r="T116" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1408</v>
       </c>
       <c r="U116" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V116" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W116" s="5"/>
+      <c r="W116" s="5">
+        <v>0</v>
+      </c>
       <c r="X116" s="1"/>
       <c r="Y116" s="5"/>
       <c r="Z116" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1408</v>
       </c>
       <c r="AA116" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -22668,26 +23496,28 @@
       <c r="F117" s="1"/>
       <c r="G117" s="5"/>
       <c r="H117" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1408</v>
       </c>
       <c r="I117" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J117" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K117" s="5"/>
+      <c r="K117" s="5">
+        <v>0</v>
+      </c>
       <c r="L117" s="1"/>
       <c r="M117" s="5"/>
       <c r="N117" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1408</v>
       </c>
       <c r="O117" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P117" s="5">
@@ -22698,26 +23528,28 @@
       <c r="R117" s="1"/>
       <c r="S117" s="5"/>
       <c r="T117" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1408</v>
       </c>
       <c r="U117" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V117" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W117" s="5"/>
+      <c r="W117" s="5">
+        <v>0</v>
+      </c>
       <c r="X117" s="1"/>
       <c r="Y117" s="5"/>
       <c r="Z117" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1408</v>
       </c>
       <c r="AA117" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -22741,26 +23573,28 @@
       <c r="F118" s="1"/>
       <c r="G118" s="5"/>
       <c r="H118" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1408</v>
       </c>
       <c r="I118" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J118" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K118" s="5"/>
+      <c r="K118" s="5">
+        <v>0</v>
+      </c>
       <c r="L118" s="1"/>
       <c r="M118" s="5"/>
       <c r="N118" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1408</v>
       </c>
       <c r="O118" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P118" s="5">
@@ -22771,26 +23605,28 @@
       <c r="R118" s="1"/>
       <c r="S118" s="5"/>
       <c r="T118" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1408</v>
       </c>
       <c r="U118" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V118" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W118" s="5"/>
+      <c r="W118" s="5">
+        <v>0</v>
+      </c>
       <c r="X118" s="1"/>
       <c r="Y118" s="5"/>
       <c r="Z118" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1408</v>
       </c>
       <c r="AA118" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -22814,26 +23650,28 @@
       <c r="F119" s="1"/>
       <c r="G119" s="5"/>
       <c r="H119" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1408</v>
       </c>
       <c r="I119" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J119" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K119" s="5"/>
+      <c r="K119" s="5">
+        <v>0</v>
+      </c>
       <c r="L119" s="1"/>
       <c r="M119" s="5"/>
       <c r="N119" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1408</v>
       </c>
       <c r="O119" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P119" s="5">
@@ -22844,26 +23682,28 @@
       <c r="R119" s="1"/>
       <c r="S119" s="5"/>
       <c r="T119" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1408</v>
       </c>
       <c r="U119" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V119" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W119" s="5"/>
+      <c r="W119" s="5">
+        <v>0</v>
+      </c>
       <c r="X119" s="1"/>
       <c r="Y119" s="5"/>
       <c r="Z119" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1408</v>
       </c>
       <c r="AA119" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -22887,26 +23727,28 @@
       <c r="F120" s="1"/>
       <c r="G120" s="5"/>
       <c r="H120" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1408</v>
       </c>
       <c r="I120" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J120" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K120" s="5"/>
+      <c r="K120" s="5">
+        <v>0</v>
+      </c>
       <c r="L120" s="1"/>
       <c r="M120" s="5"/>
       <c r="N120" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1408</v>
       </c>
       <c r="O120" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P120" s="5">
@@ -22917,26 +23759,28 @@
       <c r="R120" s="1"/>
       <c r="S120" s="5"/>
       <c r="T120" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1408</v>
       </c>
       <c r="U120" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V120" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W120" s="5"/>
+      <c r="W120" s="5">
+        <v>0</v>
+      </c>
       <c r="X120" s="1"/>
       <c r="Y120" s="5"/>
       <c r="Z120" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1408</v>
       </c>
       <c r="AA120" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -22960,26 +23804,28 @@
       <c r="F121" s="1"/>
       <c r="G121" s="5"/>
       <c r="H121" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1408</v>
       </c>
       <c r="I121" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J121" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K121" s="5"/>
+      <c r="K121" s="5">
+        <v>0</v>
+      </c>
       <c r="L121" s="1"/>
       <c r="M121" s="5"/>
       <c r="N121" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1408</v>
       </c>
       <c r="O121" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P121" s="5">
@@ -22990,26 +23836,28 @@
       <c r="R121" s="1"/>
       <c r="S121" s="5"/>
       <c r="T121" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1408</v>
       </c>
       <c r="U121" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V121" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W121" s="5"/>
+      <c r="W121" s="5">
+        <v>0</v>
+      </c>
       <c r="X121" s="1"/>
       <c r="Y121" s="5"/>
       <c r="Z121" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1408</v>
       </c>
       <c r="AA121" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -23033,26 +23881,28 @@
       <c r="F122" s="1"/>
       <c r="G122" s="5"/>
       <c r="H122" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1408</v>
       </c>
       <c r="I122" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J122" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="K122" s="5"/>
+      <c r="K122" s="5">
+        <v>0</v>
+      </c>
       <c r="L122" s="1"/>
       <c r="M122" s="5"/>
       <c r="N122" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1408</v>
       </c>
       <c r="O122" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P122" s="5">
@@ -23063,26 +23913,28 @@
       <c r="R122" s="1"/>
       <c r="S122" s="5"/>
       <c r="T122" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1408</v>
       </c>
       <c r="U122" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V122" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1408</v>
       </c>
-      <c r="W122" s="5"/>
+      <c r="W122" s="5">
+        <v>0</v>
+      </c>
       <c r="X122" s="1"/>
       <c r="Y122" s="5"/>
       <c r="Z122" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1408</v>
       </c>
       <c r="AA122" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -23597,190 +24449,10 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D55:F65 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 Z91:AA101 Z103:AA113 N115:R122 T115:X122 Z115:AA122 H115:L122 N31:R41 N43:R53 N67:R77 N79:R89 T12:X19 T21:X29 H55:L65 N55:R65 D67:F77 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D79:F89 D91:F101 H91:L101 N91:R101 T91:X101 D103:F113 H103:L113 N103:R113 T103:X113 D115:F122" name="LAS"/>
+    <protectedRange sqref="J2:L2 N3:O10 T3:U10 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 N115:R122 Z115:AA122 T12:X19 N55:R65 D67:F77 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D79:F89 D91:F101 N91:R101 T91:X101 D103:F113 H103:L113 N103:R113 T103:X113 D115:F122 D55:F65 H3:L10 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 H67:L77 H79:L89 H91:L101 H115:L122 P2:R10 N12:R19 N21:R29 N31:R41 N43:R53 N67:R77 N79:R89 V2:X10 T21:X29 T31:X41 T43:X53 T55:X65 T67:X77 T79:X89 T115:X122" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 M12:M19 S12:S19 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 G91:G101 G103:G113 Y115:Y122 G115:G122 M115:M122 S115:S122 Y12:Y19 Y21:Y29 M55:M65 S55:S65 G12:G19 M91:M101 S91:S101 Y91:Y101 M103:M113 S103:S113 Y103:Y113" name="SOURCE"/>
     <protectedRange sqref="C3:C10" name="Textbooks_1"/>
     <protectedRange sqref="C12:C19" name="Textbooks_2"/>
@@ -23805,8 +24477,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 S55:S65 M115:M122 S12:S19 M12:M19 M21:M29 G21:G29 Y12:Y19 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 M55:M65 Y21:Y29 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 S91:S101 M91:M101 G12:G19 G91:G101 G103:G113 S103:S113 M103:M113 Y91:Y101 Y103:Y113" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X12:X19 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 R91:R101 R103:R113 F103:F113 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 X21:X29 F12:F19 X91:X101 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 L55:L65 L91:L101 L103:L113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 R55:R65 F115:F122 R115:R122 L115:L122 X103:X113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 X103:X113 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 R44:R53" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
